--- a/frontend/public/data/jobs.xlsx
+++ b/frontend/public/data/jobs.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实训室-岗位-课程对照" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="能力域×岗位矩阵" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="信息缺口与补充建议" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="岗位核心能力矩阵" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="48">
+  <fonts count="54">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -335,8 +336,39 @@
       <sz val="10"/>
     </font>
     <font/>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="00BF8F00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="48">
+  <fills count="51">
     <fill>
       <patternFill/>
     </fill>
@@ -619,8 +651,26 @@
         <bgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F5496"/>
+        <bgColor rgb="002F5496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+        <bgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -776,6 +826,20 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00AAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="00AAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00AAAAAA"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -924,7 +988,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1191,6 +1255,55 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="46" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="48" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="49" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="50" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="50" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="50" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="50" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="50" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="50" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1701,7 +1814,7 @@
       </c>
       <c r="J3" s="58" t="inlineStr">
         <is>
-          <t>鸿蒙智联实训室</t>
+          <t>鸿蒙物联网智能技术实训室</t>
         </is>
       </c>
       <c r="K3" s="58" t="inlineStr">
@@ -1751,59 +1864,55 @@
       </c>
       <c r="T3" s="58" t="inlineStr">
         <is>
-          <t>空天地一体实训室</t>
+          <t>虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="U3" s="58" t="inlineStr">
         <is>
-          <t>洁净实验室1</t>
+          <t>洁净实验室</t>
         </is>
       </c>
       <c r="V3" s="58" t="inlineStr">
         <is>
-          <t>洁净实验室2</t>
+          <t>AIoT智能融合实训室</t>
         </is>
       </c>
       <c r="W3" s="58" t="inlineStr">
         <is>
-          <t>集成电路与电子信息实训室</t>
+          <t>TPU异构算力与软硬协同实训室</t>
         </is>
       </c>
       <c r="X3" s="58" t="inlineStr">
         <is>
-          <t>TPU异构算力与软硬协同实训室</t>
+          <t>卫星互联网实训室</t>
         </is>
       </c>
       <c r="Y3" s="58" t="inlineStr">
         <is>
-          <t>卫星互联网实训室</t>
+          <t>AI高端装备制造实训室</t>
         </is>
       </c>
       <c r="Z3" s="58" t="inlineStr">
         <is>
-          <t>AI高端装备制造实训室</t>
+          <t>智能交通行业应用开发实训室</t>
         </is>
       </c>
       <c r="AA3" s="58" t="inlineStr">
         <is>
-          <t>智能交通行业应用开发实训室</t>
+          <t>智能制造行业开发实训室</t>
         </is>
       </c>
       <c r="AB3" s="58" t="inlineStr">
         <is>
-          <t>智能制造行业开发实训室</t>
+          <t>电子数据取证司法鉴定实训室</t>
         </is>
       </c>
       <c r="AC3" s="58" t="inlineStr">
         <is>
-          <t>电子数据取证司法鉴定实训室</t>
-        </is>
-      </c>
-      <c r="AD3" s="58" t="inlineStr">
-        <is>
           <t>数据标注实训室</t>
         </is>
       </c>
+      <c r="AD3" s="58" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="38" t="n">
@@ -1829,35 +1938,43 @@
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="F4" s="38" t="inlineStr"/>
-      <c r="G4" s="38" t="inlineStr"/>
-      <c r="H4" s="38" t="inlineStr"/>
-      <c r="I4" s="38" t="inlineStr"/>
-      <c r="J4" s="38" t="inlineStr"/>
-      <c r="K4" s="38" t="inlineStr"/>
-      <c r="L4" s="38" t="inlineStr"/>
-      <c r="M4" s="38" t="inlineStr"/>
-      <c r="N4" s="38" t="inlineStr"/>
-      <c r="O4" s="38" t="inlineStr"/>
-      <c r="P4" s="38" t="inlineStr"/>
+      <c r="F4" s="38" t="n"/>
+      <c r="G4" s="38" t="n"/>
+      <c r="H4" s="38" t="inlineStr">
+        <is>
+          <t>◐</t>
+        </is>
+      </c>
+      <c r="I4" s="38" t="n"/>
+      <c r="J4" s="38" t="n"/>
+      <c r="K4" s="38" t="n"/>
+      <c r="L4" s="38" t="n"/>
+      <c r="M4" s="38" t="n"/>
+      <c r="N4" s="38" t="n"/>
+      <c r="O4" s="38" t="n"/>
+      <c r="P4" s="38" t="n"/>
       <c r="Q4" s="60" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="R4" s="38" t="inlineStr"/>
-      <c r="S4" s="38" t="inlineStr"/>
-      <c r="T4" s="38" t="inlineStr"/>
-      <c r="U4" s="38" t="inlineStr"/>
-      <c r="V4" s="38" t="inlineStr"/>
-      <c r="W4" s="38" t="inlineStr"/>
-      <c r="X4" s="38" t="inlineStr"/>
-      <c r="Y4" s="38" t="inlineStr"/>
-      <c r="Z4" s="38" t="inlineStr"/>
-      <c r="AA4" s="38" t="inlineStr"/>
-      <c r="AB4" s="38" t="inlineStr"/>
-      <c r="AC4" s="38" t="inlineStr"/>
-      <c r="AD4" s="61" t="inlineStr"/>
+      <c r="R4" s="38" t="n"/>
+      <c r="S4" s="38" t="n"/>
+      <c r="T4" s="38" t="n"/>
+      <c r="U4" s="38" t="n"/>
+      <c r="V4" s="38" t="n"/>
+      <c r="W4" s="38" t="inlineStr">
+        <is>
+          <t>◐</t>
+        </is>
+      </c>
+      <c r="X4" s="38" t="n"/>
+      <c r="Y4" s="38" t="n"/>
+      <c r="Z4" s="38" t="n"/>
+      <c r="AA4" s="38" t="n"/>
+      <c r="AB4" s="38" t="n"/>
+      <c r="AC4" s="38" t="n"/>
+      <c r="AD4" s="61" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="38" t="n">
@@ -1870,7 +1987,7 @@
       </c>
       <c r="C5" s="59" t="inlineStr">
         <is>
-          <t>AI芯片设计工程师</t>
+          <t>AI芯片设计（应用）工程师</t>
         </is>
       </c>
       <c r="D5" s="59" t="inlineStr">
@@ -1883,47 +2000,47 @@
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="F5" s="38" t="inlineStr"/>
-      <c r="G5" s="38" t="inlineStr"/>
-      <c r="H5" s="38" t="inlineStr"/>
-      <c r="I5" s="38" t="inlineStr"/>
-      <c r="J5" s="38" t="inlineStr"/>
-      <c r="K5" s="38" t="inlineStr"/>
-      <c r="L5" s="38" t="inlineStr"/>
-      <c r="M5" s="38" t="inlineStr"/>
-      <c r="N5" s="38" t="inlineStr"/>
-      <c r="O5" s="38" t="inlineStr"/>
-      <c r="P5" s="38" t="inlineStr"/>
-      <c r="Q5" s="38" t="inlineStr"/>
-      <c r="R5" s="38" t="inlineStr"/>
-      <c r="S5" s="38" t="inlineStr"/>
-      <c r="T5" s="38" t="inlineStr"/>
+      <c r="F5" s="38" t="n"/>
+      <c r="G5" s="38" t="n"/>
+      <c r="H5" s="38" t="n"/>
+      <c r="I5" s="38" t="n"/>
+      <c r="J5" s="38" t="n"/>
+      <c r="K5" s="38" t="n"/>
+      <c r="L5" s="38" t="n"/>
+      <c r="M5" s="38" t="n"/>
+      <c r="N5" s="38" t="n"/>
+      <c r="O5" s="38" t="n"/>
+      <c r="P5" s="38" t="n"/>
+      <c r="Q5" s="38" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="R5" s="38" t="n"/>
+      <c r="S5" s="38" t="n"/>
+      <c r="T5" s="38" t="n"/>
       <c r="U5" s="62" t="inlineStr">
         <is>
           <t>◐</t>
         </is>
       </c>
-      <c r="V5" s="62" t="inlineStr">
+      <c r="V5" s="62" t="n"/>
+      <c r="W5" s="60" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="X5" s="60" t="n"/>
+      <c r="Y5" s="38" t="inlineStr">
         <is>
           <t>◐</t>
         </is>
       </c>
-      <c r="W5" s="60" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="X5" s="60" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="Y5" s="38" t="inlineStr"/>
-      <c r="Z5" s="38" t="inlineStr"/>
-      <c r="AA5" s="38" t="inlineStr"/>
-      <c r="AB5" s="38" t="inlineStr"/>
-      <c r="AC5" s="38" t="inlineStr"/>
-      <c r="AD5" s="61" t="inlineStr"/>
+      <c r="Z5" s="38" t="n"/>
+      <c r="AA5" s="38" t="n"/>
+      <c r="AB5" s="38" t="n"/>
+      <c r="AC5" s="38" t="n"/>
+      <c r="AD5" s="61" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="38" t="n">
@@ -1949,43 +2066,43 @@
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="F6" s="38" t="inlineStr"/>
-      <c r="G6" s="38" t="inlineStr"/>
-      <c r="H6" s="38" t="inlineStr"/>
-      <c r="I6" s="38" t="inlineStr"/>
-      <c r="J6" s="38" t="inlineStr"/>
-      <c r="K6" s="38" t="inlineStr"/>
-      <c r="L6" s="38" t="inlineStr"/>
-      <c r="M6" s="38" t="inlineStr"/>
-      <c r="N6" s="38" t="inlineStr"/>
-      <c r="O6" s="38" t="inlineStr"/>
-      <c r="P6" s="38" t="inlineStr"/>
+      <c r="F6" s="38" t="n"/>
+      <c r="G6" s="38" t="n"/>
+      <c r="H6" s="38" t="n"/>
+      <c r="I6" s="38" t="n"/>
+      <c r="J6" s="38" t="n"/>
+      <c r="K6" s="38" t="n"/>
+      <c r="L6" s="38" t="n"/>
+      <c r="M6" s="38" t="n"/>
+      <c r="N6" s="38" t="n"/>
+      <c r="O6" s="38" t="n"/>
+      <c r="P6" s="38" t="n"/>
       <c r="Q6" s="60" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="R6" s="38" t="inlineStr"/>
+      <c r="R6" s="38" t="n"/>
       <c r="S6" s="62" t="inlineStr">
         <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="T6" s="38" t="n"/>
+      <c r="U6" s="38" t="n"/>
+      <c r="V6" s="38" t="n"/>
+      <c r="W6" s="38" t="inlineStr">
+        <is>
           <t>◐</t>
         </is>
       </c>
-      <c r="T6" s="38" t="inlineStr"/>
-      <c r="U6" s="38" t="inlineStr"/>
-      <c r="V6" s="38" t="inlineStr"/>
-      <c r="W6" s="38" t="inlineStr"/>
-      <c r="X6" s="62" t="inlineStr">
-        <is>
-          <t>◐</t>
-        </is>
-      </c>
-      <c r="Y6" s="38" t="inlineStr"/>
-      <c r="Z6" s="38" t="inlineStr"/>
-      <c r="AA6" s="38" t="inlineStr"/>
-      <c r="AB6" s="38" t="inlineStr"/>
-      <c r="AC6" s="38" t="inlineStr"/>
-      <c r="AD6" s="61" t="inlineStr"/>
+      <c r="X6" s="62" t="n"/>
+      <c r="Y6" s="38" t="n"/>
+      <c r="Z6" s="38" t="n"/>
+      <c r="AA6" s="38" t="n"/>
+      <c r="AB6" s="38" t="n"/>
+      <c r="AC6" s="38" t="n"/>
+      <c r="AD6" s="61" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="38" t="n">
@@ -2011,39 +2128,43 @@
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="F7" s="38" t="inlineStr"/>
-      <c r="G7" s="38" t="inlineStr"/>
-      <c r="H7" s="38" t="inlineStr"/>
-      <c r="I7" s="38" t="inlineStr"/>
-      <c r="J7" s="38" t="inlineStr"/>
-      <c r="K7" s="38" t="inlineStr"/>
-      <c r="L7" s="38" t="inlineStr"/>
-      <c r="M7" s="38" t="inlineStr"/>
-      <c r="N7" s="38" t="inlineStr"/>
-      <c r="O7" s="38" t="inlineStr"/>
-      <c r="P7" s="62" t="inlineStr">
+      <c r="F7" s="38" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="G7" s="38" t="n"/>
+      <c r="H7" s="38" t="inlineStr">
         <is>
           <t>◐</t>
         </is>
       </c>
+      <c r="I7" s="38" t="n"/>
+      <c r="J7" s="38" t="n"/>
+      <c r="K7" s="38" t="n"/>
+      <c r="L7" s="38" t="n"/>
+      <c r="M7" s="38" t="n"/>
+      <c r="N7" s="38" t="n"/>
+      <c r="O7" s="38" t="n"/>
+      <c r="P7" s="62" t="n"/>
       <c r="Q7" s="60" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="R7" s="38" t="inlineStr"/>
-      <c r="S7" s="38" t="inlineStr"/>
-      <c r="T7" s="38" t="inlineStr"/>
-      <c r="U7" s="38" t="inlineStr"/>
-      <c r="V7" s="38" t="inlineStr"/>
-      <c r="W7" s="38" t="inlineStr"/>
-      <c r="X7" s="38" t="inlineStr"/>
-      <c r="Y7" s="38" t="inlineStr"/>
-      <c r="Z7" s="38" t="inlineStr"/>
-      <c r="AA7" s="38" t="inlineStr"/>
-      <c r="AB7" s="38" t="inlineStr"/>
-      <c r="AC7" s="38" t="inlineStr"/>
-      <c r="AD7" s="61" t="inlineStr"/>
+      <c r="R7" s="38" t="n"/>
+      <c r="S7" s="38" t="n"/>
+      <c r="T7" s="38" t="n"/>
+      <c r="U7" s="38" t="n"/>
+      <c r="V7" s="38" t="n"/>
+      <c r="W7" s="38" t="n"/>
+      <c r="X7" s="38" t="n"/>
+      <c r="Y7" s="38" t="n"/>
+      <c r="Z7" s="38" t="n"/>
+      <c r="AA7" s="38" t="n"/>
+      <c r="AB7" s="38" t="n"/>
+      <c r="AC7" s="38" t="n"/>
+      <c r="AD7" s="61" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="38" t="n">
@@ -2069,39 +2190,43 @@
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="F8" s="38" t="inlineStr"/>
-      <c r="G8" s="38" t="inlineStr"/>
-      <c r="H8" s="38" t="inlineStr"/>
-      <c r="I8" s="38" t="inlineStr"/>
-      <c r="J8" s="38" t="inlineStr"/>
-      <c r="K8" s="38" t="inlineStr"/>
-      <c r="L8" s="38" t="inlineStr"/>
-      <c r="M8" s="38" t="inlineStr"/>
-      <c r="N8" s="38" t="inlineStr"/>
-      <c r="O8" s="38" t="inlineStr"/>
-      <c r="P8" s="62" t="inlineStr">
+      <c r="F8" s="38" t="inlineStr">
         <is>
           <t>◐</t>
         </is>
       </c>
+      <c r="G8" s="38" t="n"/>
+      <c r="H8" s="38" t="n"/>
+      <c r="I8" s="38" t="n"/>
+      <c r="J8" s="38" t="n"/>
+      <c r="K8" s="38" t="n"/>
+      <c r="L8" s="38" t="n"/>
+      <c r="M8" s="38" t="n"/>
+      <c r="N8" s="38" t="n"/>
+      <c r="O8" s="38" t="n"/>
+      <c r="P8" s="62" t="n"/>
       <c r="Q8" s="60" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="R8" s="38" t="inlineStr"/>
-      <c r="S8" s="38" t="inlineStr"/>
-      <c r="T8" s="38" t="inlineStr"/>
-      <c r="U8" s="38" t="inlineStr"/>
-      <c r="V8" s="38" t="inlineStr"/>
-      <c r="W8" s="38" t="inlineStr"/>
-      <c r="X8" s="38" t="inlineStr"/>
-      <c r="Y8" s="38" t="inlineStr"/>
-      <c r="Z8" s="38" t="inlineStr"/>
-      <c r="AA8" s="38" t="inlineStr"/>
-      <c r="AB8" s="38" t="inlineStr"/>
-      <c r="AC8" s="38" t="inlineStr"/>
-      <c r="AD8" s="61" t="inlineStr"/>
+      <c r="R8" s="38" t="n"/>
+      <c r="S8" s="38" t="n"/>
+      <c r="T8" s="38" t="n"/>
+      <c r="U8" s="38" t="n"/>
+      <c r="V8" s="38" t="n"/>
+      <c r="W8" s="38" t="inlineStr">
+        <is>
+          <t>◐</t>
+        </is>
+      </c>
+      <c r="X8" s="38" t="n"/>
+      <c r="Y8" s="38" t="n"/>
+      <c r="Z8" s="38" t="n"/>
+      <c r="AA8" s="38" t="n"/>
+      <c r="AB8" s="38" t="n"/>
+      <c r="AC8" s="38" t="n"/>
+      <c r="AD8" s="61" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="41" t="n">
@@ -2129,41 +2254,41 @@
       </c>
       <c r="F9" s="64" t="inlineStr">
         <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="G9" s="41" t="n"/>
+      <c r="H9" s="41" t="n"/>
+      <c r="I9" s="41" t="n"/>
+      <c r="J9" s="41" t="n"/>
+      <c r="K9" s="41" t="n"/>
+      <c r="L9" s="41" t="n"/>
+      <c r="M9" s="41" t="n"/>
+      <c r="N9" s="41" t="n"/>
+      <c r="O9" s="41" t="n"/>
+      <c r="P9" s="65" t="inlineStr">
+        <is>
           <t>◐</t>
         </is>
       </c>
-      <c r="G9" s="41" t="inlineStr"/>
-      <c r="H9" s="41" t="inlineStr"/>
-      <c r="I9" s="41" t="inlineStr"/>
-      <c r="J9" s="41" t="inlineStr"/>
-      <c r="K9" s="41" t="inlineStr"/>
-      <c r="L9" s="41" t="inlineStr"/>
-      <c r="M9" s="41" t="inlineStr"/>
-      <c r="N9" s="41" t="inlineStr"/>
-      <c r="O9" s="41" t="inlineStr"/>
-      <c r="P9" s="65" t="inlineStr">
+      <c r="Q9" s="41" t="n"/>
+      <c r="R9" s="41" t="n"/>
+      <c r="S9" s="41" t="n"/>
+      <c r="T9" s="41" t="n"/>
+      <c r="U9" s="41" t="n"/>
+      <c r="V9" s="41" t="n"/>
+      <c r="W9" s="41" t="n"/>
+      <c r="X9" s="41" t="n"/>
+      <c r="Y9" s="41" t="n"/>
+      <c r="Z9" s="41" t="n"/>
+      <c r="AA9" s="41" t="n"/>
+      <c r="AB9" s="41" t="n"/>
+      <c r="AC9" s="41" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q9" s="41" t="inlineStr"/>
-      <c r="R9" s="41" t="inlineStr"/>
-      <c r="S9" s="41" t="inlineStr"/>
-      <c r="T9" s="41" t="inlineStr"/>
-      <c r="U9" s="41" t="inlineStr"/>
-      <c r="V9" s="41" t="inlineStr"/>
-      <c r="W9" s="41" t="inlineStr"/>
-      <c r="X9" s="41" t="inlineStr"/>
-      <c r="Y9" s="41" t="inlineStr"/>
-      <c r="Z9" s="41" t="inlineStr"/>
-      <c r="AA9" s="41" t="inlineStr"/>
-      <c r="AB9" s="41" t="inlineStr"/>
-      <c r="AC9" s="41" t="inlineStr"/>
-      <c r="AD9" s="66" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
+      <c r="AD9" s="66" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="41" t="n">
@@ -2189,39 +2314,39 @@
           <t>⭐⭐</t>
         </is>
       </c>
-      <c r="F10" s="41" t="inlineStr"/>
-      <c r="G10" s="41" t="inlineStr"/>
-      <c r="H10" s="41" t="inlineStr"/>
-      <c r="I10" s="41" t="inlineStr"/>
-      <c r="J10" s="41" t="inlineStr"/>
-      <c r="K10" s="41" t="inlineStr"/>
-      <c r="L10" s="41" t="inlineStr"/>
-      <c r="M10" s="64" t="inlineStr">
+      <c r="F10" s="41" t="inlineStr">
         <is>
           <t>◐</t>
         </is>
       </c>
-      <c r="N10" s="41" t="inlineStr"/>
-      <c r="O10" s="41" t="inlineStr"/>
-      <c r="P10" s="41" t="inlineStr"/>
-      <c r="Q10" s="41" t="inlineStr"/>
-      <c r="R10" s="41" t="inlineStr"/>
-      <c r="S10" s="41" t="inlineStr"/>
-      <c r="T10" s="41" t="inlineStr"/>
-      <c r="U10" s="41" t="inlineStr"/>
-      <c r="V10" s="41" t="inlineStr"/>
-      <c r="W10" s="41" t="inlineStr"/>
-      <c r="X10" s="41" t="inlineStr"/>
-      <c r="Y10" s="41" t="inlineStr"/>
-      <c r="Z10" s="41" t="inlineStr"/>
-      <c r="AA10" s="41" t="inlineStr"/>
-      <c r="AB10" s="41" t="inlineStr"/>
-      <c r="AC10" s="41" t="inlineStr"/>
-      <c r="AD10" s="66" t="inlineStr">
+      <c r="G10" s="41" t="n"/>
+      <c r="H10" s="41" t="n"/>
+      <c r="I10" s="41" t="n"/>
+      <c r="J10" s="41" t="n"/>
+      <c r="K10" s="41" t="n"/>
+      <c r="L10" s="41" t="n"/>
+      <c r="M10" s="64" t="n"/>
+      <c r="N10" s="41" t="n"/>
+      <c r="O10" s="41" t="n"/>
+      <c r="P10" s="41" t="n"/>
+      <c r="Q10" s="41" t="n"/>
+      <c r="R10" s="41" t="n"/>
+      <c r="S10" s="41" t="n"/>
+      <c r="T10" s="41" t="n"/>
+      <c r="U10" s="41" t="n"/>
+      <c r="V10" s="41" t="n"/>
+      <c r="W10" s="41" t="n"/>
+      <c r="X10" s="41" t="n"/>
+      <c r="Y10" s="41" t="n"/>
+      <c r="Z10" s="41" t="n"/>
+      <c r="AA10" s="41" t="n"/>
+      <c r="AB10" s="41" t="n"/>
+      <c r="AC10" s="41" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
+      <c r="AD10" s="66" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="41" t="n">
@@ -2252,38 +2377,38 @@
           <t>●</t>
         </is>
       </c>
-      <c r="G11" s="41" t="inlineStr"/>
-      <c r="H11" s="41" t="inlineStr"/>
-      <c r="I11" s="41" t="inlineStr"/>
-      <c r="J11" s="41" t="inlineStr"/>
-      <c r="K11" s="41" t="inlineStr"/>
-      <c r="L11" s="41" t="inlineStr"/>
-      <c r="M11" s="41" t="inlineStr"/>
-      <c r="N11" s="41" t="inlineStr"/>
+      <c r="G11" s="41" t="n"/>
+      <c r="H11" s="41" t="n"/>
+      <c r="I11" s="41" t="n"/>
+      <c r="J11" s="41" t="n"/>
+      <c r="K11" s="41" t="n"/>
+      <c r="L11" s="41" t="n"/>
+      <c r="M11" s="41" t="n"/>
+      <c r="N11" s="41" t="n"/>
       <c r="O11" s="64" t="inlineStr">
         <is>
           <t>◐</t>
         </is>
       </c>
-      <c r="P11" s="41" t="inlineStr"/>
-      <c r="Q11" s="41" t="inlineStr"/>
-      <c r="R11" s="41" t="inlineStr"/>
-      <c r="S11" s="41" t="inlineStr"/>
-      <c r="T11" s="41" t="inlineStr"/>
-      <c r="U11" s="41" t="inlineStr"/>
-      <c r="V11" s="41" t="inlineStr"/>
-      <c r="W11" s="41" t="inlineStr"/>
-      <c r="X11" s="41" t="inlineStr"/>
-      <c r="Y11" s="41" t="inlineStr"/>
-      <c r="Z11" s="41" t="inlineStr"/>
-      <c r="AA11" s="41" t="inlineStr"/>
-      <c r="AB11" s="41" t="inlineStr"/>
-      <c r="AC11" s="41" t="inlineStr"/>
-      <c r="AD11" s="66" t="inlineStr">
+      <c r="P11" s="41" t="n"/>
+      <c r="Q11" s="41" t="n"/>
+      <c r="R11" s="41" t="n"/>
+      <c r="S11" s="41" t="n"/>
+      <c r="T11" s="41" t="n"/>
+      <c r="U11" s="41" t="n"/>
+      <c r="V11" s="41" t="n"/>
+      <c r="W11" s="41" t="n"/>
+      <c r="X11" s="41" t="n"/>
+      <c r="Y11" s="41" t="n"/>
+      <c r="Z11" s="41" t="n"/>
+      <c r="AA11" s="41" t="n"/>
+      <c r="AB11" s="41" t="n"/>
+      <c r="AC11" s="41" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
+      <c r="AD11" s="66" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="41" t="n">
@@ -2309,39 +2434,43 @@
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="F12" s="41" t="inlineStr"/>
-      <c r="G12" s="41" t="inlineStr"/>
-      <c r="H12" s="41" t="inlineStr"/>
-      <c r="I12" s="41" t="inlineStr"/>
-      <c r="J12" s="41" t="inlineStr"/>
-      <c r="K12" s="41" t="inlineStr"/>
-      <c r="L12" s="41" t="inlineStr"/>
-      <c r="M12" s="41" t="inlineStr"/>
-      <c r="N12" s="41" t="inlineStr"/>
-      <c r="O12" s="65" t="inlineStr">
+      <c r="F12" s="41" t="inlineStr">
+        <is>
+          <t>◐</t>
+        </is>
+      </c>
+      <c r="G12" s="41" t="n"/>
+      <c r="H12" s="41" t="n"/>
+      <c r="I12" s="41" t="n"/>
+      <c r="J12" s="41" t="n"/>
+      <c r="K12" s="41" t="n"/>
+      <c r="L12" s="41" t="n"/>
+      <c r="M12" s="41" t="inlineStr">
+        <is>
+          <t>◐</t>
+        </is>
+      </c>
+      <c r="N12" s="41" t="n"/>
+      <c r="O12" s="65" t="n"/>
+      <c r="P12" s="41" t="n"/>
+      <c r="Q12" s="41" t="n"/>
+      <c r="R12" s="41" t="n"/>
+      <c r="S12" s="41" t="n"/>
+      <c r="T12" s="41" t="n"/>
+      <c r="U12" s="41" t="n"/>
+      <c r="V12" s="41" t="n"/>
+      <c r="W12" s="41" t="n"/>
+      <c r="X12" s="41" t="n"/>
+      <c r="Y12" s="41" t="n"/>
+      <c r="Z12" s="41" t="n"/>
+      <c r="AA12" s="41" t="n"/>
+      <c r="AB12" s="41" t="n"/>
+      <c r="AC12" s="41" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P12" s="41" t="inlineStr"/>
-      <c r="Q12" s="41" t="inlineStr"/>
-      <c r="R12" s="41" t="inlineStr"/>
-      <c r="S12" s="41" t="inlineStr"/>
-      <c r="T12" s="41" t="inlineStr"/>
-      <c r="U12" s="41" t="inlineStr"/>
-      <c r="V12" s="41" t="inlineStr"/>
-      <c r="W12" s="41" t="inlineStr"/>
-      <c r="X12" s="41" t="inlineStr"/>
-      <c r="Y12" s="41" t="inlineStr"/>
-      <c r="Z12" s="41" t="inlineStr"/>
-      <c r="AA12" s="41" t="inlineStr"/>
-      <c r="AB12" s="41" t="inlineStr"/>
-      <c r="AC12" s="41" t="inlineStr"/>
-      <c r="AD12" s="67" t="inlineStr">
-        <is>
-          <t>◐</t>
-        </is>
-      </c>
+      <c r="AD12" s="67" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="41" t="n">
@@ -2367,39 +2496,43 @@
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="F13" s="41" t="inlineStr"/>
-      <c r="G13" s="41" t="inlineStr"/>
-      <c r="H13" s="41" t="inlineStr"/>
-      <c r="I13" s="41" t="inlineStr"/>
-      <c r="J13" s="41" t="inlineStr"/>
-      <c r="K13" s="41" t="inlineStr"/>
-      <c r="L13" s="41" t="inlineStr"/>
-      <c r="M13" s="41" t="inlineStr"/>
+      <c r="F13" s="41" t="n"/>
+      <c r="G13" s="41" t="n"/>
+      <c r="H13" s="41" t="n"/>
+      <c r="I13" s="41" t="n"/>
+      <c r="J13" s="41" t="n"/>
+      <c r="K13" s="41" t="n"/>
+      <c r="L13" s="41" t="n"/>
+      <c r="M13" s="41" t="inlineStr">
+        <is>
+          <t>◐</t>
+        </is>
+      </c>
       <c r="N13" s="65" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="O13" s="41" t="inlineStr"/>
-      <c r="P13" s="41" t="inlineStr"/>
-      <c r="Q13" s="41" t="inlineStr"/>
-      <c r="R13" s="41" t="inlineStr"/>
-      <c r="S13" s="41" t="inlineStr"/>
-      <c r="T13" s="41" t="inlineStr"/>
-      <c r="U13" s="41" t="inlineStr"/>
-      <c r="V13" s="41" t="inlineStr"/>
-      <c r="W13" s="41" t="inlineStr"/>
-      <c r="X13" s="41" t="inlineStr"/>
-      <c r="Y13" s="41" t="inlineStr"/>
-      <c r="Z13" s="41" t="inlineStr"/>
-      <c r="AA13" s="41" t="inlineStr"/>
-      <c r="AB13" s="41" t="inlineStr"/>
-      <c r="AC13" s="65" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="AD13" s="61" t="inlineStr"/>
+      <c r="O13" s="41" t="n"/>
+      <c r="P13" s="41" t="n"/>
+      <c r="Q13" s="41" t="n"/>
+      <c r="R13" s="41" t="n"/>
+      <c r="S13" s="41" t="n"/>
+      <c r="T13" s="41" t="n"/>
+      <c r="U13" s="41" t="n"/>
+      <c r="V13" s="41" t="n"/>
+      <c r="W13" s="41" t="n"/>
+      <c r="X13" s="41" t="n"/>
+      <c r="Y13" s="41" t="n"/>
+      <c r="Z13" s="41" t="n"/>
+      <c r="AA13" s="41" t="n"/>
+      <c r="AB13" s="41" t="inlineStr">
+        <is>
+          <t>◐</t>
+        </is>
+      </c>
+      <c r="AC13" s="65" t="n"/>
+      <c r="AD13" s="61" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="44" t="n">
@@ -2430,46 +2563,38 @@
           <t>●</t>
         </is>
       </c>
-      <c r="G14" s="70" t="inlineStr">
+      <c r="G14" s="70" t="n"/>
+      <c r="H14" s="44" t="n"/>
+      <c r="I14" s="70" t="n"/>
+      <c r="J14" s="44" t="n"/>
+      <c r="K14" s="44" t="n"/>
+      <c r="L14" s="44" t="n"/>
+      <c r="M14" s="44" t="n"/>
+      <c r="N14" s="44" t="n"/>
+      <c r="O14" s="44" t="n"/>
+      <c r="P14" s="44" t="n"/>
+      <c r="Q14" s="70" t="inlineStr">
         <is>
           <t>◐</t>
         </is>
       </c>
-      <c r="H14" s="44" t="inlineStr"/>
-      <c r="I14" s="70" t="inlineStr">
-        <is>
-          <t>◐</t>
-        </is>
-      </c>
-      <c r="J14" s="44" t="inlineStr"/>
-      <c r="K14" s="44" t="inlineStr"/>
-      <c r="L14" s="44" t="inlineStr"/>
-      <c r="M14" s="44" t="inlineStr"/>
-      <c r="N14" s="44" t="inlineStr"/>
-      <c r="O14" s="44" t="inlineStr"/>
-      <c r="P14" s="44" t="inlineStr"/>
-      <c r="Q14" s="70" t="inlineStr">
-        <is>
-          <t>◐</t>
-        </is>
-      </c>
       <c r="R14" s="69" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="S14" s="44" t="inlineStr"/>
-      <c r="T14" s="44" t="inlineStr"/>
-      <c r="U14" s="44" t="inlineStr"/>
-      <c r="V14" s="44" t="inlineStr"/>
-      <c r="W14" s="44" t="inlineStr"/>
-      <c r="X14" s="44" t="inlineStr"/>
-      <c r="Y14" s="44" t="inlineStr"/>
-      <c r="Z14" s="44" t="inlineStr"/>
-      <c r="AA14" s="44" t="inlineStr"/>
-      <c r="AB14" s="44" t="inlineStr"/>
-      <c r="AC14" s="44" t="inlineStr"/>
-      <c r="AD14" s="61" t="inlineStr"/>
+      <c r="S14" s="44" t="n"/>
+      <c r="T14" s="44" t="n"/>
+      <c r="U14" s="44" t="n"/>
+      <c r="V14" s="44" t="n"/>
+      <c r="W14" s="44" t="n"/>
+      <c r="X14" s="44" t="n"/>
+      <c r="Y14" s="44" t="n"/>
+      <c r="Z14" s="44" t="n"/>
+      <c r="AA14" s="44" t="n"/>
+      <c r="AB14" s="44" t="n"/>
+      <c r="AC14" s="44" t="n"/>
+      <c r="AD14" s="61" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="44" t="n">
@@ -2495,43 +2620,43 @@
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="F15" s="44" t="inlineStr"/>
+      <c r="F15" s="44" t="n"/>
       <c r="G15" s="69" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="H15" s="44" t="inlineStr"/>
+      <c r="H15" s="44" t="n"/>
       <c r="I15" s="69" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="J15" s="44" t="inlineStr"/>
-      <c r="K15" s="44" t="inlineStr"/>
-      <c r="L15" s="44" t="inlineStr"/>
-      <c r="M15" s="44" t="inlineStr"/>
-      <c r="N15" s="44" t="inlineStr"/>
-      <c r="O15" s="44" t="inlineStr"/>
-      <c r="P15" s="44" t="inlineStr"/>
-      <c r="Q15" s="44" t="inlineStr"/>
+      <c r="J15" s="44" t="n"/>
+      <c r="K15" s="44" t="n"/>
+      <c r="L15" s="44" t="n"/>
+      <c r="M15" s="44" t="n"/>
+      <c r="N15" s="44" t="n"/>
+      <c r="O15" s="44" t="n"/>
+      <c r="P15" s="44" t="n"/>
+      <c r="Q15" s="44" t="n"/>
       <c r="R15" s="70" t="inlineStr">
         <is>
           <t>◐</t>
         </is>
       </c>
-      <c r="S15" s="44" t="inlineStr"/>
-      <c r="T15" s="44" t="inlineStr"/>
-      <c r="U15" s="44" t="inlineStr"/>
-      <c r="V15" s="44" t="inlineStr"/>
-      <c r="W15" s="44" t="inlineStr"/>
-      <c r="X15" s="44" t="inlineStr"/>
-      <c r="Y15" s="44" t="inlineStr"/>
-      <c r="Z15" s="44" t="inlineStr"/>
-      <c r="AA15" s="44" t="inlineStr"/>
-      <c r="AB15" s="44" t="inlineStr"/>
-      <c r="AC15" s="44" t="inlineStr"/>
-      <c r="AD15" s="61" t="inlineStr"/>
+      <c r="S15" s="44" t="n"/>
+      <c r="T15" s="44" t="n"/>
+      <c r="U15" s="44" t="n"/>
+      <c r="V15" s="44" t="n"/>
+      <c r="W15" s="44" t="n"/>
+      <c r="X15" s="44" t="n"/>
+      <c r="Y15" s="44" t="n"/>
+      <c r="Z15" s="44" t="n"/>
+      <c r="AA15" s="44" t="n"/>
+      <c r="AB15" s="44" t="n"/>
+      <c r="AC15" s="44" t="n"/>
+      <c r="AD15" s="61" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="44" t="n">
@@ -2557,47 +2682,43 @@
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="F16" s="69" t="inlineStr">
+      <c r="F16" s="69" t="n"/>
+      <c r="G16" s="69" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="G16" s="69" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="H16" s="70" t="inlineStr">
+      <c r="H16" s="70" t="n"/>
+      <c r="I16" s="44" t="n"/>
+      <c r="J16" s="44" t="n"/>
+      <c r="K16" s="44" t="n"/>
+      <c r="L16" s="44" t="n"/>
+      <c r="M16" s="44" t="n"/>
+      <c r="N16" s="44" t="n"/>
+      <c r="O16" s="44" t="n"/>
+      <c r="P16" s="44" t="n"/>
+      <c r="Q16" s="44" t="n"/>
+      <c r="R16" s="44" t="inlineStr">
         <is>
           <t>◐</t>
         </is>
       </c>
-      <c r="I16" s="44" t="inlineStr"/>
-      <c r="J16" s="44" t="inlineStr"/>
-      <c r="K16" s="44" t="inlineStr"/>
-      <c r="L16" s="44" t="inlineStr"/>
-      <c r="M16" s="44" t="inlineStr"/>
-      <c r="N16" s="44" t="inlineStr"/>
-      <c r="O16" s="44" t="inlineStr"/>
-      <c r="P16" s="44" t="inlineStr"/>
-      <c r="Q16" s="44" t="inlineStr"/>
-      <c r="R16" s="44" t="inlineStr"/>
-      <c r="S16" s="44" t="inlineStr"/>
-      <c r="T16" s="44" t="inlineStr"/>
-      <c r="U16" s="44" t="inlineStr"/>
-      <c r="V16" s="44" t="inlineStr"/>
-      <c r="W16" s="44" t="inlineStr"/>
-      <c r="X16" s="44" t="inlineStr"/>
-      <c r="Y16" s="44" t="inlineStr"/>
+      <c r="S16" s="44" t="n"/>
+      <c r="T16" s="44" t="n"/>
+      <c r="U16" s="44" t="n"/>
+      <c r="V16" s="44" t="n"/>
+      <c r="W16" s="44" t="n"/>
+      <c r="X16" s="44" t="n"/>
+      <c r="Y16" s="44" t="n"/>
       <c r="Z16" s="70" t="inlineStr">
         <is>
           <t>◐</t>
         </is>
       </c>
-      <c r="AA16" s="44" t="inlineStr"/>
-      <c r="AB16" s="44" t="inlineStr"/>
-      <c r="AC16" s="44" t="inlineStr"/>
-      <c r="AD16" s="61" t="inlineStr"/>
+      <c r="AA16" s="44" t="n"/>
+      <c r="AB16" s="44" t="n"/>
+      <c r="AC16" s="44" t="n"/>
+      <c r="AD16" s="61" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="44" t="n">
@@ -2623,47 +2744,47 @@
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="F17" s="44" t="inlineStr"/>
-      <c r="G17" s="44" t="inlineStr"/>
-      <c r="H17" s="44" t="inlineStr"/>
-      <c r="I17" s="44" t="inlineStr"/>
-      <c r="J17" s="44" t="inlineStr"/>
-      <c r="K17" s="44" t="inlineStr"/>
+      <c r="F17" s="44" t="n"/>
+      <c r="G17" s="44" t="n"/>
+      <c r="H17" s="44" t="n"/>
+      <c r="I17" s="44" t="n"/>
+      <c r="J17" s="44" t="n"/>
+      <c r="K17" s="44" t="n"/>
       <c r="L17" s="69" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="M17" s="44" t="inlineStr"/>
-      <c r="N17" s="44" t="inlineStr"/>
-      <c r="O17" s="44" t="inlineStr"/>
+      <c r="M17" s="44" t="n"/>
+      <c r="N17" s="44" t="n"/>
+      <c r="O17" s="44" t="n"/>
       <c r="P17" s="70" t="inlineStr">
         <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="Q17" s="69" t="n"/>
+      <c r="R17" s="44" t="n"/>
+      <c r="S17" s="70" t="inlineStr">
+        <is>
           <t>◐</t>
         </is>
       </c>
-      <c r="Q17" s="69" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="R17" s="44" t="inlineStr"/>
-      <c r="S17" s="70" t="inlineStr">
+      <c r="T17" s="44" t="inlineStr">
         <is>
           <t>◐</t>
         </is>
       </c>
-      <c r="T17" s="44" t="inlineStr"/>
-      <c r="U17" s="44" t="inlineStr"/>
-      <c r="V17" s="44" t="inlineStr"/>
-      <c r="W17" s="44" t="inlineStr"/>
-      <c r="X17" s="44" t="inlineStr"/>
-      <c r="Y17" s="44" t="inlineStr"/>
-      <c r="Z17" s="44" t="inlineStr"/>
-      <c r="AA17" s="44" t="inlineStr"/>
-      <c r="AB17" s="44" t="inlineStr"/>
-      <c r="AC17" s="44" t="inlineStr"/>
-      <c r="AD17" s="61" t="inlineStr"/>
+      <c r="U17" s="44" t="n"/>
+      <c r="V17" s="44" t="n"/>
+      <c r="W17" s="44" t="n"/>
+      <c r="X17" s="44" t="n"/>
+      <c r="Y17" s="44" t="n"/>
+      <c r="Z17" s="44" t="n"/>
+      <c r="AA17" s="44" t="n"/>
+      <c r="AB17" s="44" t="n"/>
+      <c r="AC17" s="44" t="n"/>
+      <c r="AD17" s="61" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="44" t="n">
@@ -2689,47 +2810,47 @@
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="F18" s="44" t="inlineStr"/>
-      <c r="G18" s="44" t="inlineStr"/>
-      <c r="H18" s="44" t="inlineStr"/>
-      <c r="I18" s="44" t="inlineStr"/>
-      <c r="J18" s="44" t="inlineStr"/>
-      <c r="K18" s="44" t="inlineStr"/>
-      <c r="L18" s="44" t="inlineStr"/>
-      <c r="M18" s="44" t="inlineStr"/>
-      <c r="N18" s="44" t="inlineStr"/>
-      <c r="O18" s="44" t="inlineStr"/>
+      <c r="F18" s="44" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="G18" s="44" t="n"/>
+      <c r="H18" s="44" t="n"/>
+      <c r="I18" s="44" t="n"/>
+      <c r="J18" s="44" t="n"/>
+      <c r="K18" s="44" t="n"/>
+      <c r="L18" s="44" t="n"/>
+      <c r="M18" s="44" t="n"/>
+      <c r="N18" s="44" t="n"/>
+      <c r="O18" s="44" t="n"/>
       <c r="P18" s="69" t="inlineStr">
         <is>
+          <t>◐</t>
+        </is>
+      </c>
+      <c r="Q18" s="69" t="inlineStr">
+        <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q18" s="69" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="R18" s="44" t="inlineStr"/>
-      <c r="S18" s="70" t="inlineStr">
+      <c r="R18" s="44" t="n"/>
+      <c r="S18" s="70" t="n"/>
+      <c r="T18" s="44" t="n"/>
+      <c r="U18" s="44" t="n"/>
+      <c r="V18" s="44" t="n"/>
+      <c r="W18" s="44" t="inlineStr">
         <is>
           <t>◐</t>
         </is>
       </c>
-      <c r="T18" s="44" t="inlineStr"/>
-      <c r="U18" s="44" t="inlineStr"/>
-      <c r="V18" s="44" t="inlineStr"/>
-      <c r="W18" s="44" t="inlineStr"/>
-      <c r="X18" s="44" t="inlineStr"/>
-      <c r="Y18" s="44" t="inlineStr"/>
-      <c r="Z18" s="44" t="inlineStr"/>
-      <c r="AA18" s="44" t="inlineStr"/>
-      <c r="AB18" s="44" t="inlineStr"/>
-      <c r="AC18" s="44" t="inlineStr"/>
-      <c r="AD18" s="71" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+      <c r="X18" s="44" t="n"/>
+      <c r="Y18" s="44" t="n"/>
+      <c r="Z18" s="44" t="n"/>
+      <c r="AA18" s="44" t="n"/>
+      <c r="AB18" s="44" t="n"/>
+      <c r="AC18" s="44" t="n"/>
+      <c r="AD18" s="71" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="47" t="n">
@@ -2760,38 +2881,38 @@
           <t>●</t>
         </is>
       </c>
-      <c r="G19" s="47" t="inlineStr"/>
-      <c r="H19" s="47" t="inlineStr"/>
-      <c r="I19" s="47" t="inlineStr"/>
-      <c r="J19" s="47" t="inlineStr"/>
-      <c r="K19" s="47" t="inlineStr"/>
-      <c r="L19" s="47" t="inlineStr"/>
-      <c r="M19" s="47" t="inlineStr"/>
-      <c r="N19" s="47" t="inlineStr"/>
-      <c r="O19" s="47" t="inlineStr"/>
+      <c r="G19" s="47" t="n"/>
+      <c r="H19" s="47" t="n"/>
+      <c r="I19" s="47" t="n"/>
+      <c r="J19" s="47" t="n"/>
+      <c r="K19" s="47" t="n"/>
+      <c r="L19" s="47" t="n"/>
+      <c r="M19" s="47" t="n"/>
+      <c r="N19" s="47" t="n"/>
+      <c r="O19" s="47" t="n"/>
       <c r="P19" s="73" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q19" s="47" t="inlineStr"/>
+      <c r="Q19" s="47" t="n"/>
       <c r="R19" s="74" t="inlineStr">
         <is>
           <t>◐</t>
         </is>
       </c>
-      <c r="S19" s="47" t="inlineStr"/>
-      <c r="T19" s="47" t="inlineStr"/>
-      <c r="U19" s="47" t="inlineStr"/>
-      <c r="V19" s="47" t="inlineStr"/>
-      <c r="W19" s="47" t="inlineStr"/>
-      <c r="X19" s="47" t="inlineStr"/>
-      <c r="Y19" s="47" t="inlineStr"/>
-      <c r="Z19" s="47" t="inlineStr"/>
-      <c r="AA19" s="47" t="inlineStr"/>
-      <c r="AB19" s="47" t="inlineStr"/>
-      <c r="AC19" s="47" t="inlineStr"/>
-      <c r="AD19" s="61" t="inlineStr"/>
+      <c r="S19" s="47" t="n"/>
+      <c r="T19" s="47" t="n"/>
+      <c r="U19" s="47" t="n"/>
+      <c r="V19" s="47" t="n"/>
+      <c r="W19" s="47" t="n"/>
+      <c r="X19" s="47" t="n"/>
+      <c r="Y19" s="47" t="n"/>
+      <c r="Z19" s="47" t="n"/>
+      <c r="AA19" s="47" t="n"/>
+      <c r="AB19" s="47" t="n"/>
+      <c r="AC19" s="47" t="n"/>
+      <c r="AD19" s="61" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="47" t="n">
@@ -2817,39 +2938,39 @@
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="F20" s="74" t="inlineStr">
+      <c r="F20" s="74" t="n"/>
+      <c r="G20" s="47" t="n"/>
+      <c r="H20" s="47" t="n"/>
+      <c r="I20" s="47" t="n"/>
+      <c r="J20" s="47" t="n"/>
+      <c r="K20" s="47" t="n"/>
+      <c r="L20" s="47" t="n"/>
+      <c r="M20" s="47" t="n"/>
+      <c r="N20" s="47" t="n"/>
+      <c r="O20" s="47" t="n"/>
+      <c r="P20" s="47" t="n"/>
+      <c r="Q20" s="73" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="R20" s="47" t="n"/>
+      <c r="S20" s="47" t="n"/>
+      <c r="T20" s="47" t="n"/>
+      <c r="U20" s="47" t="n"/>
+      <c r="V20" s="47" t="n"/>
+      <c r="W20" s="47" t="inlineStr">
         <is>
           <t>◐</t>
         </is>
       </c>
-      <c r="G20" s="47" t="inlineStr"/>
-      <c r="H20" s="47" t="inlineStr"/>
-      <c r="I20" s="47" t="inlineStr"/>
-      <c r="J20" s="47" t="inlineStr"/>
-      <c r="K20" s="47" t="inlineStr"/>
-      <c r="L20" s="47" t="inlineStr"/>
-      <c r="M20" s="47" t="inlineStr"/>
-      <c r="N20" s="47" t="inlineStr"/>
-      <c r="O20" s="47" t="inlineStr"/>
-      <c r="P20" s="47" t="inlineStr"/>
-      <c r="Q20" s="73" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="R20" s="47" t="inlineStr"/>
-      <c r="S20" s="47" t="inlineStr"/>
-      <c r="T20" s="47" t="inlineStr"/>
-      <c r="U20" s="47" t="inlineStr"/>
-      <c r="V20" s="47" t="inlineStr"/>
-      <c r="W20" s="47" t="inlineStr"/>
-      <c r="X20" s="47" t="inlineStr"/>
-      <c r="Y20" s="47" t="inlineStr"/>
-      <c r="Z20" s="47" t="inlineStr"/>
-      <c r="AA20" s="47" t="inlineStr"/>
-      <c r="AB20" s="47" t="inlineStr"/>
-      <c r="AC20" s="47" t="inlineStr"/>
-      <c r="AD20" s="61" t="inlineStr"/>
+      <c r="X20" s="47" t="n"/>
+      <c r="Y20" s="47" t="n"/>
+      <c r="Z20" s="47" t="n"/>
+      <c r="AA20" s="47" t="n"/>
+      <c r="AB20" s="47" t="n"/>
+      <c r="AC20" s="47" t="n"/>
+      <c r="AD20" s="61" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="47" t="n">
@@ -2880,34 +3001,54 @@
           <t>●</t>
         </is>
       </c>
-      <c r="G21" s="47" t="inlineStr"/>
-      <c r="H21" s="74" t="inlineStr">
+      <c r="G21" s="47" t="n"/>
+      <c r="H21" s="74" t="n"/>
+      <c r="I21" s="47" t="n"/>
+      <c r="J21" s="47" t="inlineStr">
         <is>
           <t>◐</t>
         </is>
       </c>
-      <c r="I21" s="47" t="inlineStr"/>
-      <c r="J21" s="47" t="inlineStr"/>
-      <c r="K21" s="47" t="inlineStr"/>
-      <c r="L21" s="47" t="inlineStr"/>
-      <c r="M21" s="47" t="inlineStr"/>
-      <c r="N21" s="47" t="inlineStr"/>
-      <c r="O21" s="47" t="inlineStr"/>
-      <c r="P21" s="47" t="inlineStr"/>
-      <c r="Q21" s="47" t="inlineStr"/>
-      <c r="R21" s="47" t="inlineStr"/>
-      <c r="S21" s="47" t="inlineStr"/>
-      <c r="T21" s="47" t="inlineStr"/>
-      <c r="U21" s="47" t="inlineStr"/>
-      <c r="V21" s="47" t="inlineStr"/>
-      <c r="W21" s="47" t="inlineStr"/>
-      <c r="X21" s="47" t="inlineStr"/>
-      <c r="Y21" s="47" t="inlineStr"/>
-      <c r="Z21" s="47" t="inlineStr"/>
-      <c r="AA21" s="47" t="inlineStr"/>
-      <c r="AB21" s="47" t="inlineStr"/>
-      <c r="AC21" s="47" t="inlineStr"/>
-      <c r="AD21" s="61" t="inlineStr"/>
+      <c r="K21" s="47" t="n"/>
+      <c r="L21" s="47" t="n"/>
+      <c r="M21" s="47" t="n"/>
+      <c r="N21" s="47" t="n"/>
+      <c r="O21" s="47" t="n"/>
+      <c r="P21" s="47" t="n"/>
+      <c r="Q21" s="47" t="n"/>
+      <c r="R21" s="47" t="n"/>
+      <c r="S21" s="47" t="n"/>
+      <c r="T21" s="47" t="n"/>
+      <c r="U21" s="47" t="n"/>
+      <c r="V21" s="47" t="inlineStr">
+        <is>
+          <t>◐</t>
+        </is>
+      </c>
+      <c r="W21" s="47" t="n"/>
+      <c r="X21" s="47" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="Y21" s="47" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="Z21" s="47" t="inlineStr">
+        <is>
+          <t>◐</t>
+        </is>
+      </c>
+      <c r="AA21" s="47" t="inlineStr">
+        <is>
+          <t>◐</t>
+        </is>
+      </c>
+      <c r="AB21" s="47" t="n"/>
+      <c r="AC21" s="47" t="n"/>
+      <c r="AD21" s="61" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="47" t="n">
@@ -2933,43 +3074,43 @@
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="F22" s="73" t="inlineStr">
+      <c r="F22" s="73" t="n"/>
+      <c r="G22" s="47" t="n"/>
+      <c r="H22" s="47" t="inlineStr">
+        <is>
+          <t>◐</t>
+        </is>
+      </c>
+      <c r="I22" s="47" t="n"/>
+      <c r="J22" s="47" t="n"/>
+      <c r="K22" s="47" t="n"/>
+      <c r="L22" s="47" t="n"/>
+      <c r="M22" s="47" t="n"/>
+      <c r="N22" s="47" t="n"/>
+      <c r="O22" s="47" t="n"/>
+      <c r="P22" s="47" t="n"/>
+      <c r="Q22" s="47" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="G22" s="47" t="inlineStr"/>
-      <c r="H22" s="47" t="inlineStr"/>
-      <c r="I22" s="47" t="inlineStr"/>
-      <c r="J22" s="47" t="inlineStr"/>
-      <c r="K22" s="47" t="inlineStr"/>
-      <c r="L22" s="47" t="inlineStr"/>
-      <c r="M22" s="47" t="inlineStr"/>
-      <c r="N22" s="47" t="inlineStr"/>
-      <c r="O22" s="47" t="inlineStr"/>
-      <c r="P22" s="47" t="inlineStr"/>
-      <c r="Q22" s="47" t="inlineStr"/>
-      <c r="R22" s="47" t="inlineStr"/>
-      <c r="S22" s="47" t="inlineStr"/>
-      <c r="T22" s="47" t="inlineStr"/>
-      <c r="U22" s="47" t="inlineStr"/>
-      <c r="V22" s="47" t="inlineStr"/>
-      <c r="W22" s="47" t="inlineStr"/>
-      <c r="X22" s="47" t="inlineStr"/>
-      <c r="Y22" s="47" t="inlineStr"/>
-      <c r="Z22" s="47" t="inlineStr"/>
-      <c r="AA22" s="74" t="inlineStr">
+      <c r="R22" s="47" t="n"/>
+      <c r="S22" s="47" t="n"/>
+      <c r="T22" s="47" t="n"/>
+      <c r="U22" s="47" t="n"/>
+      <c r="V22" s="47" t="n"/>
+      <c r="W22" s="47" t="inlineStr">
         <is>
           <t>◐</t>
         </is>
       </c>
-      <c r="AB22" s="74" t="inlineStr">
-        <is>
-          <t>◐</t>
-        </is>
-      </c>
-      <c r="AC22" s="47" t="inlineStr"/>
-      <c r="AD22" s="61" t="inlineStr"/>
+      <c r="X22" s="47" t="n"/>
+      <c r="Y22" s="47" t="n"/>
+      <c r="Z22" s="47" t="n"/>
+      <c r="AA22" s="74" t="n"/>
+      <c r="AB22" s="74" t="n"/>
+      <c r="AC22" s="47" t="n"/>
+      <c r="AD22" s="61" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="47" t="n">
@@ -3000,34 +3141,38 @@
           <t>◐</t>
         </is>
       </c>
-      <c r="G23" s="47" t="inlineStr"/>
-      <c r="H23" s="47" t="inlineStr"/>
-      <c r="I23" s="47" t="inlineStr"/>
-      <c r="J23" s="47" t="inlineStr"/>
-      <c r="K23" s="47" t="inlineStr"/>
-      <c r="L23" s="47" t="inlineStr"/>
-      <c r="M23" s="47" t="inlineStr"/>
-      <c r="N23" s="47" t="inlineStr"/>
-      <c r="O23" s="47" t="inlineStr"/>
-      <c r="P23" s="47" t="inlineStr"/>
-      <c r="Q23" s="47" t="inlineStr"/>
+      <c r="G23" s="47" t="n"/>
+      <c r="H23" s="47" t="n"/>
+      <c r="I23" s="47" t="n"/>
+      <c r="J23" s="47" t="n"/>
+      <c r="K23" s="47" t="n"/>
+      <c r="L23" s="47" t="n"/>
+      <c r="M23" s="47" t="n"/>
+      <c r="N23" s="47" t="n"/>
+      <c r="O23" s="47" t="inlineStr">
+        <is>
+          <t>◐</t>
+        </is>
+      </c>
+      <c r="P23" s="47" t="n"/>
+      <c r="Q23" s="47" t="n"/>
       <c r="R23" s="73" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="S23" s="47" t="inlineStr"/>
-      <c r="T23" s="47" t="inlineStr"/>
-      <c r="U23" s="47" t="inlineStr"/>
-      <c r="V23" s="47" t="inlineStr"/>
-      <c r="W23" s="47" t="inlineStr"/>
-      <c r="X23" s="47" t="inlineStr"/>
-      <c r="Y23" s="47" t="inlineStr"/>
-      <c r="Z23" s="47" t="inlineStr"/>
-      <c r="AA23" s="47" t="inlineStr"/>
-      <c r="AB23" s="47" t="inlineStr"/>
-      <c r="AC23" s="47" t="inlineStr"/>
-      <c r="AD23" s="61" t="inlineStr"/>
+      <c r="S23" s="47" t="n"/>
+      <c r="T23" s="47" t="n"/>
+      <c r="U23" s="47" t="n"/>
+      <c r="V23" s="47" t="n"/>
+      <c r="W23" s="47" t="n"/>
+      <c r="X23" s="47" t="n"/>
+      <c r="Y23" s="47" t="n"/>
+      <c r="Z23" s="47" t="n"/>
+      <c r="AA23" s="47" t="n"/>
+      <c r="AB23" s="47" t="n"/>
+      <c r="AC23" s="47" t="n"/>
+      <c r="AD23" s="61" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="50" t="n">
@@ -3058,38 +3203,54 @@
           <t>●</t>
         </is>
       </c>
-      <c r="G24" s="50" t="inlineStr"/>
-      <c r="H24" s="76" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="I24" s="50" t="inlineStr"/>
+      <c r="G24" s="50" t="n"/>
+      <c r="H24" s="76" t="n"/>
+      <c r="I24" s="50" t="n"/>
       <c r="J24" s="77" t="inlineStr">
         <is>
           <t>◐</t>
         </is>
       </c>
-      <c r="K24" s="50" t="inlineStr"/>
-      <c r="L24" s="50" t="inlineStr"/>
-      <c r="M24" s="50" t="inlineStr"/>
-      <c r="N24" s="50" t="inlineStr"/>
-      <c r="O24" s="50" t="inlineStr"/>
-      <c r="P24" s="50" t="inlineStr"/>
-      <c r="Q24" s="50" t="inlineStr"/>
-      <c r="R24" s="50" t="inlineStr"/>
-      <c r="S24" s="50" t="inlineStr"/>
-      <c r="T24" s="50" t="inlineStr"/>
-      <c r="U24" s="50" t="inlineStr"/>
-      <c r="V24" s="50" t="inlineStr"/>
-      <c r="W24" s="50" t="inlineStr"/>
-      <c r="X24" s="50" t="inlineStr"/>
-      <c r="Y24" s="50" t="inlineStr"/>
-      <c r="Z24" s="50" t="inlineStr"/>
-      <c r="AA24" s="50" t="inlineStr"/>
-      <c r="AB24" s="50" t="inlineStr"/>
-      <c r="AC24" s="50" t="inlineStr"/>
-      <c r="AD24" s="61" t="inlineStr"/>
+      <c r="K24" s="50" t="n"/>
+      <c r="L24" s="50" t="n"/>
+      <c r="M24" s="50" t="n"/>
+      <c r="N24" s="50" t="n"/>
+      <c r="O24" s="50" t="n"/>
+      <c r="P24" s="50" t="n"/>
+      <c r="Q24" s="50" t="n"/>
+      <c r="R24" s="50" t="n"/>
+      <c r="S24" s="50" t="n"/>
+      <c r="T24" s="50" t="n"/>
+      <c r="U24" s="50" t="n"/>
+      <c r="V24" s="50" t="inlineStr">
+        <is>
+          <t>◐</t>
+        </is>
+      </c>
+      <c r="W24" s="50" t="n"/>
+      <c r="X24" s="50" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="Y24" s="50" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="Z24" s="50" t="inlineStr">
+        <is>
+          <t>◐</t>
+        </is>
+      </c>
+      <c r="AA24" s="50" t="inlineStr">
+        <is>
+          <t>◐</t>
+        </is>
+      </c>
+      <c r="AB24" s="50" t="n"/>
+      <c r="AC24" s="50" t="n"/>
+      <c r="AD24" s="61" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="50" t="n">
@@ -3120,34 +3281,38 @@
           <t>●</t>
         </is>
       </c>
-      <c r="G25" s="50" t="inlineStr"/>
-      <c r="H25" s="50" t="inlineStr"/>
-      <c r="I25" s="50" t="inlineStr"/>
-      <c r="J25" s="50" t="inlineStr"/>
-      <c r="K25" s="50" t="inlineStr"/>
-      <c r="L25" s="50" t="inlineStr"/>
-      <c r="M25" s="50" t="inlineStr"/>
-      <c r="N25" s="50" t="inlineStr"/>
-      <c r="O25" s="50" t="inlineStr"/>
+      <c r="G25" s="50" t="n"/>
+      <c r="H25" s="50" t="n"/>
+      <c r="I25" s="50" t="inlineStr">
+        <is>
+          <t>◐</t>
+        </is>
+      </c>
+      <c r="J25" s="50" t="n"/>
+      <c r="K25" s="50" t="n"/>
+      <c r="L25" s="50" t="n"/>
+      <c r="M25" s="50" t="n"/>
+      <c r="N25" s="50" t="n"/>
+      <c r="O25" s="50" t="n"/>
       <c r="P25" s="76" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q25" s="50" t="inlineStr"/>
-      <c r="R25" s="50" t="inlineStr"/>
-      <c r="S25" s="50" t="inlineStr"/>
-      <c r="T25" s="50" t="inlineStr"/>
-      <c r="U25" s="50" t="inlineStr"/>
-      <c r="V25" s="50" t="inlineStr"/>
-      <c r="W25" s="50" t="inlineStr"/>
-      <c r="X25" s="50" t="inlineStr"/>
-      <c r="Y25" s="50" t="inlineStr"/>
-      <c r="Z25" s="50" t="inlineStr"/>
-      <c r="AA25" s="50" t="inlineStr"/>
-      <c r="AB25" s="50" t="inlineStr"/>
-      <c r="AC25" s="50" t="inlineStr"/>
-      <c r="AD25" s="61" t="inlineStr"/>
+      <c r="Q25" s="50" t="n"/>
+      <c r="R25" s="50" t="n"/>
+      <c r="S25" s="50" t="n"/>
+      <c r="T25" s="50" t="n"/>
+      <c r="U25" s="50" t="n"/>
+      <c r="V25" s="50" t="n"/>
+      <c r="W25" s="50" t="n"/>
+      <c r="X25" s="50" t="n"/>
+      <c r="Y25" s="50" t="n"/>
+      <c r="Z25" s="50" t="n"/>
+      <c r="AA25" s="50" t="n"/>
+      <c r="AB25" s="50" t="n"/>
+      <c r="AC25" s="50" t="n"/>
+      <c r="AD25" s="61" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="50" t="n">
@@ -3160,7 +3325,7 @@
       </c>
       <c r="C26" s="75" t="inlineStr">
         <is>
-          <t>具身智能算法工程师</t>
+          <t>虚拟仿真工程师</t>
         </is>
       </c>
       <c r="D26" s="75" t="inlineStr">
@@ -3173,43 +3338,47 @@
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="F26" s="50" t="inlineStr"/>
-      <c r="G26" s="50" t="inlineStr"/>
-      <c r="H26" s="50" t="inlineStr"/>
-      <c r="I26" s="50" t="inlineStr"/>
-      <c r="J26" s="50" t="inlineStr"/>
-      <c r="K26" s="50" t="inlineStr"/>
+      <c r="F26" s="50" t="n"/>
+      <c r="G26" s="50" t="n"/>
+      <c r="H26" s="50" t="n"/>
+      <c r="I26" s="50" t="n"/>
+      <c r="J26" s="50" t="n"/>
+      <c r="K26" s="50" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="L26" s="76" t="inlineStr">
         <is>
+          <t>◐</t>
+        </is>
+      </c>
+      <c r="M26" s="50" t="n"/>
+      <c r="N26" s="50" t="n"/>
+      <c r="O26" s="50" t="n"/>
+      <c r="P26" s="50" t="n"/>
+      <c r="Q26" s="50" t="n"/>
+      <c r="R26" s="50" t="n"/>
+      <c r="S26" s="78" t="n"/>
+      <c r="T26" s="50" t="inlineStr">
+        <is>
           <t>●</t>
         </is>
       </c>
-      <c r="M26" s="50" t="inlineStr"/>
-      <c r="N26" s="50" t="inlineStr"/>
-      <c r="O26" s="50" t="inlineStr"/>
-      <c r="P26" s="50" t="inlineStr"/>
-      <c r="Q26" s="50" t="inlineStr"/>
-      <c r="R26" s="50" t="inlineStr"/>
-      <c r="S26" s="78" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T26" s="50" t="inlineStr"/>
-      <c r="U26" s="50" t="inlineStr"/>
-      <c r="V26" s="50" t="inlineStr"/>
-      <c r="W26" s="50" t="inlineStr"/>
-      <c r="X26" s="50" t="inlineStr"/>
-      <c r="Y26" s="50" t="inlineStr"/>
+      <c r="U26" s="50" t="n"/>
+      <c r="V26" s="50" t="n"/>
+      <c r="W26" s="50" t="n"/>
+      <c r="X26" s="50" t="n"/>
+      <c r="Y26" s="50" t="n"/>
       <c r="Z26" s="77" t="inlineStr">
         <is>
           <t>◐</t>
         </is>
       </c>
-      <c r="AA26" s="50" t="inlineStr"/>
-      <c r="AB26" s="50" t="inlineStr"/>
-      <c r="AC26" s="50" t="inlineStr"/>
-      <c r="AD26" s="61" t="inlineStr"/>
+      <c r="AA26" s="50" t="n"/>
+      <c r="AB26" s="50" t="n"/>
+      <c r="AC26" s="50" t="n"/>
+      <c r="AD26" s="61" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="50" t="n">
@@ -3235,47 +3404,47 @@
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="F27" s="50" t="inlineStr"/>
+      <c r="F27" s="50" t="n"/>
       <c r="G27" s="76" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="H27" s="50" t="inlineStr"/>
-      <c r="I27" s="50" t="inlineStr"/>
-      <c r="J27" s="50" t="inlineStr"/>
+      <c r="H27" s="50" t="n"/>
+      <c r="I27" s="50" t="n"/>
+      <c r="J27" s="50" t="n"/>
       <c r="K27" s="78" t="inlineStr">
         <is>
+          <t>◐</t>
+        </is>
+      </c>
+      <c r="L27" s="50" t="n"/>
+      <c r="M27" s="50" t="n"/>
+      <c r="N27" s="50" t="n"/>
+      <c r="O27" s="50" t="n"/>
+      <c r="P27" s="50" t="n"/>
+      <c r="Q27" s="50" t="n"/>
+      <c r="R27" s="50" t="n"/>
+      <c r="S27" s="78" t="n"/>
+      <c r="T27" s="50" t="n"/>
+      <c r="U27" s="50" t="n"/>
+      <c r="V27" s="50" t="n"/>
+      <c r="W27" s="50" t="n"/>
+      <c r="X27" s="50" t="inlineStr">
+        <is>
           <t>○</t>
         </is>
       </c>
-      <c r="L27" s="50" t="inlineStr"/>
-      <c r="M27" s="50" t="inlineStr"/>
-      <c r="N27" s="50" t="inlineStr"/>
-      <c r="O27" s="50" t="inlineStr"/>
-      <c r="P27" s="50" t="inlineStr"/>
-      <c r="Q27" s="50" t="inlineStr"/>
-      <c r="R27" s="50" t="inlineStr"/>
-      <c r="S27" s="78" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T27" s="50" t="inlineStr"/>
-      <c r="U27" s="50" t="inlineStr"/>
-      <c r="V27" s="50" t="inlineStr"/>
-      <c r="W27" s="50" t="inlineStr"/>
-      <c r="X27" s="50" t="inlineStr"/>
-      <c r="Y27" s="50" t="inlineStr"/>
-      <c r="Z27" s="50" t="inlineStr"/>
-      <c r="AA27" s="76" t="inlineStr">
+      <c r="Y27" s="50" t="n"/>
+      <c r="Z27" s="50" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="AB27" s="50" t="inlineStr"/>
-      <c r="AC27" s="50" t="inlineStr"/>
-      <c r="AD27" s="61" t="inlineStr"/>
+      <c r="AA27" s="76" t="n"/>
+      <c r="AB27" s="50" t="n"/>
+      <c r="AC27" s="50" t="n"/>
+      <c r="AD27" s="61" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="50" t="n">
@@ -3301,39 +3470,39 @@
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="F28" s="77" t="inlineStr">
-        <is>
-          <t>◐</t>
-        </is>
-      </c>
-      <c r="G28" s="50" t="inlineStr"/>
-      <c r="H28" s="50" t="inlineStr"/>
-      <c r="I28" s="50" t="inlineStr"/>
-      <c r="J28" s="50" t="inlineStr"/>
-      <c r="K28" s="50" t="inlineStr"/>
-      <c r="L28" s="50" t="inlineStr"/>
-      <c r="M28" s="50" t="inlineStr"/>
-      <c r="N28" s="50" t="inlineStr"/>
-      <c r="O28" s="50" t="inlineStr"/>
-      <c r="P28" s="50" t="inlineStr"/>
-      <c r="Q28" s="50" t="inlineStr"/>
-      <c r="R28" s="50" t="inlineStr"/>
+      <c r="F28" s="77" t="n"/>
+      <c r="G28" s="50" t="n"/>
+      <c r="H28" s="50" t="n"/>
+      <c r="I28" s="50" t="n"/>
+      <c r="J28" s="50" t="n"/>
+      <c r="K28" s="50" t="n"/>
+      <c r="L28" s="50" t="n"/>
+      <c r="M28" s="50" t="n"/>
+      <c r="N28" s="50" t="n"/>
+      <c r="O28" s="50" t="n"/>
+      <c r="P28" s="50" t="n"/>
+      <c r="Q28" s="50" t="n"/>
+      <c r="R28" s="50" t="n"/>
       <c r="S28" s="76" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="T28" s="50" t="inlineStr"/>
-      <c r="U28" s="50" t="inlineStr"/>
-      <c r="V28" s="50" t="inlineStr"/>
-      <c r="W28" s="50" t="inlineStr"/>
-      <c r="X28" s="50" t="inlineStr"/>
-      <c r="Y28" s="50" t="inlineStr"/>
-      <c r="Z28" s="50" t="inlineStr"/>
-      <c r="AA28" s="50" t="inlineStr"/>
-      <c r="AB28" s="50" t="inlineStr"/>
-      <c r="AC28" s="50" t="inlineStr"/>
-      <c r="AD28" s="61" t="inlineStr"/>
+      <c r="T28" s="50" t="n"/>
+      <c r="U28" s="50" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="V28" s="50" t="n"/>
+      <c r="W28" s="50" t="n"/>
+      <c r="X28" s="50" t="n"/>
+      <c r="Y28" s="50" t="n"/>
+      <c r="Z28" s="50" t="n"/>
+      <c r="AA28" s="50" t="n"/>
+      <c r="AB28" s="50" t="n"/>
+      <c r="AC28" s="50" t="n"/>
+      <c r="AD28" s="61" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="53" t="n">
@@ -3359,39 +3528,35 @@
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="F29" s="53" t="inlineStr"/>
-      <c r="G29" s="53" t="inlineStr"/>
-      <c r="H29" s="53" t="inlineStr"/>
-      <c r="I29" s="53" t="inlineStr"/>
-      <c r="J29" s="53" t="inlineStr"/>
-      <c r="K29" s="53" t="inlineStr"/>
+      <c r="F29" s="53" t="n"/>
+      <c r="G29" s="53" t="n"/>
+      <c r="H29" s="53" t="n"/>
+      <c r="I29" s="53" t="n"/>
+      <c r="J29" s="53" t="n"/>
+      <c r="K29" s="53" t="n"/>
       <c r="L29" s="80" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="M29" s="53" t="inlineStr"/>
-      <c r="N29" s="53" t="inlineStr"/>
-      <c r="O29" s="53" t="inlineStr"/>
-      <c r="P29" s="53" t="inlineStr"/>
-      <c r="Q29" s="53" t="inlineStr"/>
-      <c r="R29" s="53" t="inlineStr"/>
-      <c r="S29" s="53" t="inlineStr"/>
-      <c r="T29" s="53" t="inlineStr"/>
-      <c r="U29" s="53" t="inlineStr"/>
-      <c r="V29" s="53" t="inlineStr"/>
-      <c r="W29" s="53" t="inlineStr"/>
-      <c r="X29" s="53" t="inlineStr"/>
-      <c r="Y29" s="53" t="inlineStr"/>
-      <c r="Z29" s="53" t="inlineStr"/>
-      <c r="AA29" s="53" t="inlineStr"/>
-      <c r="AB29" s="80" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="AC29" s="53" t="inlineStr"/>
-      <c r="AD29" s="61" t="inlineStr"/>
+      <c r="M29" s="53" t="n"/>
+      <c r="N29" s="53" t="n"/>
+      <c r="O29" s="53" t="n"/>
+      <c r="P29" s="53" t="n"/>
+      <c r="Q29" s="53" t="n"/>
+      <c r="R29" s="53" t="n"/>
+      <c r="S29" s="53" t="n"/>
+      <c r="T29" s="53" t="n"/>
+      <c r="U29" s="53" t="n"/>
+      <c r="V29" s="53" t="n"/>
+      <c r="W29" s="53" t="n"/>
+      <c r="X29" s="53" t="n"/>
+      <c r="Y29" s="53" t="n"/>
+      <c r="Z29" s="53" t="n"/>
+      <c r="AA29" s="53" t="n"/>
+      <c r="AB29" s="80" t="n"/>
+      <c r="AC29" s="53" t="n"/>
+      <c r="AD29" s="61" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="53" t="n">
@@ -3417,43 +3582,39 @@
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="F30" s="53" t="inlineStr"/>
+      <c r="F30" s="53" t="n"/>
       <c r="G30" s="81" t="inlineStr">
         <is>
           <t>◐</t>
         </is>
       </c>
-      <c r="H30" s="53" t="inlineStr"/>
-      <c r="I30" s="53" t="inlineStr"/>
-      <c r="J30" s="53" t="inlineStr"/>
-      <c r="K30" s="53" t="inlineStr"/>
+      <c r="H30" s="53" t="n"/>
+      <c r="I30" s="53" t="n"/>
+      <c r="J30" s="53" t="n"/>
+      <c r="K30" s="53" t="n"/>
       <c r="L30" s="80" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="M30" s="53" t="inlineStr"/>
-      <c r="N30" s="53" t="inlineStr"/>
-      <c r="O30" s="53" t="inlineStr"/>
-      <c r="P30" s="53" t="inlineStr"/>
-      <c r="Q30" s="53" t="inlineStr"/>
-      <c r="R30" s="53" t="inlineStr"/>
-      <c r="S30" s="82" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T30" s="53" t="inlineStr"/>
-      <c r="U30" s="53" t="inlineStr"/>
-      <c r="V30" s="53" t="inlineStr"/>
-      <c r="W30" s="53" t="inlineStr"/>
-      <c r="X30" s="53" t="inlineStr"/>
-      <c r="Y30" s="53" t="inlineStr"/>
-      <c r="Z30" s="53" t="inlineStr"/>
-      <c r="AA30" s="53" t="inlineStr"/>
-      <c r="AB30" s="53" t="inlineStr"/>
-      <c r="AC30" s="53" t="inlineStr"/>
-      <c r="AD30" s="61" t="inlineStr"/>
+      <c r="M30" s="53" t="n"/>
+      <c r="N30" s="53" t="n"/>
+      <c r="O30" s="53" t="n"/>
+      <c r="P30" s="53" t="n"/>
+      <c r="Q30" s="53" t="n"/>
+      <c r="R30" s="53" t="n"/>
+      <c r="S30" s="82" t="n"/>
+      <c r="T30" s="53" t="n"/>
+      <c r="U30" s="53" t="n"/>
+      <c r="V30" s="53" t="n"/>
+      <c r="W30" s="53" t="n"/>
+      <c r="X30" s="53" t="n"/>
+      <c r="Y30" s="53" t="n"/>
+      <c r="Z30" s="53" t="n"/>
+      <c r="AA30" s="53" t="n"/>
+      <c r="AB30" s="53" t="n"/>
+      <c r="AC30" s="53" t="n"/>
+      <c r="AD30" s="61" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="53" t="n">
@@ -3479,39 +3640,39 @@
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="F31" s="53" t="inlineStr"/>
-      <c r="G31" s="53" t="inlineStr"/>
-      <c r="H31" s="53" t="inlineStr"/>
-      <c r="I31" s="53" t="inlineStr"/>
-      <c r="J31" s="53" t="inlineStr"/>
-      <c r="K31" s="53" t="inlineStr"/>
+      <c r="F31" s="53" t="inlineStr">
+        <is>
+          <t>◐</t>
+        </is>
+      </c>
+      <c r="G31" s="53" t="n"/>
+      <c r="H31" s="53" t="n"/>
+      <c r="I31" s="53" t="n"/>
+      <c r="J31" s="53" t="n"/>
+      <c r="K31" s="53" t="n"/>
       <c r="L31" s="80" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="M31" s="53" t="inlineStr"/>
-      <c r="N31" s="53" t="inlineStr"/>
-      <c r="O31" s="53" t="inlineStr"/>
-      <c r="P31" s="53" t="inlineStr"/>
-      <c r="Q31" s="53" t="inlineStr"/>
-      <c r="R31" s="53" t="inlineStr"/>
-      <c r="S31" s="53" t="inlineStr"/>
-      <c r="T31" s="53" t="inlineStr"/>
-      <c r="U31" s="53" t="inlineStr"/>
-      <c r="V31" s="53" t="inlineStr"/>
-      <c r="W31" s="82" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="X31" s="53" t="inlineStr"/>
-      <c r="Y31" s="53" t="inlineStr"/>
-      <c r="Z31" s="53" t="inlineStr"/>
-      <c r="AA31" s="53" t="inlineStr"/>
-      <c r="AB31" s="53" t="inlineStr"/>
-      <c r="AC31" s="53" t="inlineStr"/>
-      <c r="AD31" s="61" t="inlineStr"/>
+      <c r="M31" s="53" t="n"/>
+      <c r="N31" s="53" t="n"/>
+      <c r="O31" s="53" t="n"/>
+      <c r="P31" s="53" t="n"/>
+      <c r="Q31" s="53" t="n"/>
+      <c r="R31" s="53" t="n"/>
+      <c r="S31" s="53" t="n"/>
+      <c r="T31" s="53" t="n"/>
+      <c r="U31" s="53" t="n"/>
+      <c r="V31" s="53" t="n"/>
+      <c r="W31" s="82" t="n"/>
+      <c r="X31" s="53" t="n"/>
+      <c r="Y31" s="53" t="n"/>
+      <c r="Z31" s="53" t="n"/>
+      <c r="AA31" s="53" t="n"/>
+      <c r="AB31" s="53" t="n"/>
+      <c r="AC31" s="53" t="n"/>
+      <c r="AD31" s="61" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="53" t="n">
@@ -3537,43 +3698,47 @@
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="F32" s="53" t="inlineStr"/>
-      <c r="G32" s="53" t="inlineStr"/>
-      <c r="H32" s="53" t="inlineStr"/>
-      <c r="I32" s="53" t="inlineStr"/>
-      <c r="J32" s="53" t="inlineStr"/>
-      <c r="K32" s="53" t="inlineStr"/>
+      <c r="F32" s="53" t="n"/>
+      <c r="G32" s="53" t="n"/>
+      <c r="H32" s="53" t="n"/>
+      <c r="I32" s="53" t="n"/>
+      <c r="J32" s="53" t="n"/>
+      <c r="K32" s="53" t="n"/>
       <c r="L32" s="80" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="M32" s="53" t="inlineStr"/>
-      <c r="N32" s="53" t="inlineStr"/>
-      <c r="O32" s="53" t="inlineStr"/>
-      <c r="P32" s="53" t="inlineStr"/>
-      <c r="Q32" s="53" t="inlineStr"/>
-      <c r="R32" s="53" t="inlineStr"/>
-      <c r="S32" s="53" t="inlineStr"/>
-      <c r="T32" s="53" t="inlineStr"/>
-      <c r="U32" s="53" t="inlineStr"/>
-      <c r="V32" s="53" t="inlineStr"/>
-      <c r="W32" s="53" t="inlineStr"/>
-      <c r="X32" s="53" t="inlineStr"/>
-      <c r="Y32" s="53" t="inlineStr"/>
-      <c r="Z32" s="81" t="inlineStr">
+      <c r="M32" s="53" t="n"/>
+      <c r="N32" s="53" t="n"/>
+      <c r="O32" s="53" t="n"/>
+      <c r="P32" s="53" t="n"/>
+      <c r="Q32" s="53" t="n"/>
+      <c r="R32" s="53" t="n"/>
+      <c r="S32" s="53" t="n"/>
+      <c r="T32" s="53" t="inlineStr">
         <is>
           <t>◐</t>
         </is>
       </c>
-      <c r="AA32" s="53" t="inlineStr"/>
-      <c r="AB32" s="80" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="AC32" s="53" t="inlineStr"/>
-      <c r="AD32" s="61" t="inlineStr"/>
+      <c r="U32" s="53" t="n"/>
+      <c r="V32" s="53" t="n"/>
+      <c r="W32" s="53" t="n"/>
+      <c r="X32" s="53" t="n"/>
+      <c r="Y32" s="53" t="inlineStr">
+        <is>
+          <t>◐</t>
+        </is>
+      </c>
+      <c r="Z32" s="81" t="n"/>
+      <c r="AA32" s="53" t="inlineStr">
+        <is>
+          <t>◐</t>
+        </is>
+      </c>
+      <c r="AB32" s="80" t="n"/>
+      <c r="AC32" s="53" t="n"/>
+      <c r="AD32" s="61" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="53" t="n">
@@ -3612,11 +3777,7 @@
       </c>
       <c r="M33" s="53" t="n"/>
       <c r="N33" s="53" t="n"/>
-      <c r="O33" s="53" t="inlineStr">
-        <is>
-          <t>◐</t>
-        </is>
-      </c>
+      <c r="O33" s="53" t="n"/>
       <c r="P33" s="53" t="n"/>
       <c r="Q33" s="53" t="n"/>
       <c r="R33" s="53" t="n"/>
@@ -3625,27 +3786,15 @@
       <c r="U33" s="53" t="n"/>
       <c r="V33" s="53" t="n"/>
       <c r="W33" s="53" t="n"/>
-      <c r="X33" s="53" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="Y33" s="53" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="Z33" s="53" t="inlineStr">
+      <c r="X33" s="53" t="n"/>
+      <c r="Y33" s="53" t="n"/>
+      <c r="Z33" s="53" t="n"/>
+      <c r="AA33" s="53" t="inlineStr">
         <is>
           <t>◐</t>
         </is>
       </c>
-      <c r="AA33" s="53" t="n"/>
-      <c r="AB33" s="53" t="inlineStr">
-        <is>
-          <t>◐</t>
-        </is>
-      </c>
+      <c r="AB33" s="53" t="n"/>
       <c r="AC33" s="53" t="n"/>
       <c r="AD33" s="53" t="n"/>
     </row>
@@ -3940,7 +4089,7 @@
       </c>
       <c r="B8" s="39" t="inlineStr">
         <is>
-          <t>AI芯片设计工程师</t>
+          <t>AI芯片设计（应用）工程师</t>
         </is>
       </c>
       <c r="C8" s="38" t="inlineStr">
@@ -3973,7 +4122,7 @@
       </c>
       <c r="H8" s="39" t="inlineStr">
         <is>
-          <t>集成电路与电子信息实训室、TPU异构算力与软硬协同实训室</t>
+          <t>AIoT智能融合实训室、TPU异构算力与软硬协同实训室</t>
         </is>
       </c>
       <c r="I8" s="39" t="inlineStr">
@@ -3988,7 +4137,7 @@
       </c>
       <c r="B9" s="39" t="inlineStr">
         <is>
-          <t>AI芯片设计工程师</t>
+          <t>AI芯片设计（应用）工程师</t>
         </is>
       </c>
       <c r="C9" s="38" t="inlineStr">
@@ -4021,7 +4170,7 @@
       </c>
       <c r="H9" s="39" t="inlineStr">
         <is>
-          <t>集成电路与电子信息实训室</t>
+          <t>AIoT智能融合实训室</t>
         </is>
       </c>
       <c r="I9" s="39" t="inlineStr">
@@ -4036,7 +4185,7 @@
       </c>
       <c r="B10" s="39" t="inlineStr">
         <is>
-          <t>AI芯片设计工程师</t>
+          <t>AI芯片设计（应用）工程师</t>
         </is>
       </c>
       <c r="C10" s="38" t="inlineStr">
@@ -4069,7 +4218,7 @@
       </c>
       <c r="H10" s="39" t="inlineStr">
         <is>
-          <t>洁净实验室1、洁净实验室2、集成电路与电子信息实训室、集成电路与电子信息实训室</t>
+          <t>洁净实验室、洁净实验室、AIoT智能融合实训室、AIoT智能融合实训室</t>
         </is>
       </c>
       <c r="I10" s="39" t="inlineStr">
@@ -4210,7 +4359,7 @@
       </c>
       <c r="H13" s="39" t="inlineStr">
         <is>
-          <t>AI4S实训室、空天地一体实训室</t>
+          <t>AI4S实训室、虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="I13" s="39" t="inlineStr">
@@ -6688,7 +6837,7 @@
       </c>
       <c r="H66" s="51" t="inlineStr">
         <is>
-          <t>人工智能应用开发实训室、智能边缘计算应用开发实训室、人工智能应用开发实训室、智能边缘计算应用开发实训室、鸿蒙智联实训室</t>
+          <t>人工智能应用开发实训室、智能边缘计算应用开发实训室、人工智能应用开发实训室、智能边缘计算应用开发实训室、鸿蒙物联网智能技术实训室</t>
         </is>
       </c>
       <c r="I66" s="51" t="inlineStr">
@@ -6778,7 +6927,7 @@
       </c>
       <c r="H68" s="51" t="inlineStr">
         <is>
-          <t>人工智能应用开发实训室、鸿蒙智联实训室</t>
+          <t>人工智能应用开发实训室、鸿蒙物联网智能技术实训室</t>
         </is>
       </c>
       <c r="I68" s="51" t="inlineStr">
@@ -6937,7 +7086,7 @@
       </c>
       <c r="B72" s="51" t="inlineStr">
         <is>
-          <t>具身智能算法工程师</t>
+          <t>虚拟仿真工程师</t>
         </is>
       </c>
       <c r="C72" s="50" t="inlineStr">
@@ -6947,35 +7096,35 @@
       </c>
       <c r="D72" s="52" t="inlineStr">
         <is>
-          <t>具身智能</t>
+          <t>数字孪生</t>
         </is>
       </c>
       <c r="E72" s="51" t="inlineStr">
         <is>
-          <t>【感知融合】了解机器人传感器（视觉/力觉/IMU）基础
-【运动控制】了解机器人运动学和控制基础</t>
+          <t>【3D建模】了解三维建模基础（Blender/3ds Max等工具）
+【场景搭建】了解虚拟仿真场景的基本构成和搭建流程</t>
         </is>
       </c>
       <c r="F72" s="51" t="inlineStr">
         <is>
-          <t>【感知融合】实现多传感器融合的机器人感知系统
-【运动控制】实现机器人轨迹规划和运动控制算法</t>
+          <t>【数字孪生】能构建物理设备的数字孪生模型，实现虚实映射和数据同步
+【仿真引擎】掌握Unity/Unreal Engine等仿真引擎的开发与部署</t>
         </is>
       </c>
       <c r="G72" s="51" t="inlineStr">
         <is>
-          <t>【感知融合】设计端到端具身智能感知架构
-【运动控制】设计复杂环境下的自主运动控制系统</t>
+          <t>【系统仿真】能设计大型系统的数字孪生方案（智慧城市/智能制造）
+【仿真平台】能搭建企业级虚拟仿真平台，实现多场景仿真协同</t>
         </is>
       </c>
       <c r="H72" s="51" t="inlineStr">
         <is>
-          <t>具身智能实训室、具身智能实训室、AI高端装备制造实训室</t>
+          <t>虚拟仿真创新实训室、具身智能实训室</t>
         </is>
       </c>
       <c r="I72" s="51" t="inlineStr">
         <is>
-          <t>机器人技术实践</t>
+          <t>数字孪生与3D建模基础、仿真引擎开发与部署</t>
         </is>
       </c>
     </row>
@@ -6985,7 +7134,7 @@
       </c>
       <c r="B73" s="51" t="inlineStr">
         <is>
-          <t>具身智能算法工程师</t>
+          <t>虚拟仿真工程师</t>
         </is>
       </c>
       <c r="C73" s="50" t="inlineStr">
@@ -6995,35 +7144,35 @@
       </c>
       <c r="D73" s="52" t="inlineStr">
         <is>
-          <t>学习决策</t>
+          <t>仿真算法</t>
         </is>
       </c>
       <c r="E73" s="51" t="inlineStr">
         <is>
-          <t>【强化学习】了解强化学习在机器人中的应用
-【仿真训练】了解机器人仿真环境（Isaac Gym等）</t>
+          <t>【物理仿真】了解物理引擎基本原理（碰撞检测/刚体动力学）
+【AI仿真】了解AI算法在仿真环境中的应用方法</t>
         </is>
       </c>
       <c r="F73" s="51" t="inlineStr">
         <is>
-          <t>【强化学习】训练机器人完成抓取/导航等任务的RL策略
-【仿真训练】在仿真环境中训练和验证机器人算法</t>
+          <t>【算法集成】能将AI算法（视觉/路径规划/控制）集成到仿真系统中
+【场景验证】能在仿真环境中验证算法效果并迭代优化</t>
         </is>
       </c>
       <c r="G73" s="51" t="inlineStr">
         <is>
-          <t>【强化学习】研发端到端具身智能学习算法
-【仿真训练】设计sim-to-real迁移方案</t>
+          <t>【算法优化】能基于仿真数据反哺算法训练和参数调优
+【虚实闭环】能建立仿真-实物的闭环验证体系</t>
         </is>
       </c>
       <c r="H73" s="51" t="inlineStr">
         <is>
-          <t>具身智能实训室、具身智能实训室、AI4S实训室</t>
+          <t>虚拟仿真创新实训室、AI4S实训室</t>
         </is>
       </c>
       <c r="I73" s="51" t="inlineStr">
         <is>
-          <t>强化学习、机器人技术实践</t>
+          <t>物理仿真与AI算法集成、仿真环境算法验证</t>
         </is>
       </c>
     </row>
@@ -7033,7 +7182,7 @@
       </c>
       <c r="B74" s="51" t="inlineStr">
         <is>
-          <t>具身智能算法工程师</t>
+          <t>虚拟仿真工程师</t>
         </is>
       </c>
       <c r="C74" s="50" t="inlineStr">
@@ -7043,32 +7192,35 @@
       </c>
       <c r="D74" s="52" t="inlineStr">
         <is>
-          <t>人机交互</t>
+          <t>交互设计</t>
         </is>
       </c>
       <c r="E74" s="51" t="inlineStr">
         <is>
-          <t>【交互设计】了解人机交互和协作基础</t>
+          <t>【交互设计】了解人机交互和VR/AR基础技术
+【UI/UX】了解虚拟仿真系统的界面设计和用户体验基础</t>
         </is>
       </c>
       <c r="F74" s="51" t="inlineStr">
         <is>
-          <t>【交互设计】实现人机协作的安全交互方案</t>
+          <t>【VR/AR开发】能开发VR/AR交互应用（HTC Vive/Oculus等平台）
+【可视化】能实现仿真数据的多维可视化和交互式展示</t>
         </is>
       </c>
       <c r="G74" s="51" t="inlineStr">
         <is>
-          <t>【交互设计】设计自然交互的具身智能系统</t>
+          <t>【沉浸式体验】能设计大型沉浸式仿真体验系统
+【交互创新】能探索新型人机交互技术在仿真中的应用</t>
         </is>
       </c>
       <c r="H74" s="51" t="inlineStr">
         <is>
-          <t>具身智能实训室</t>
+          <t>虚拟仿真创新实训室、AIGC视觉传达实训室</t>
         </is>
       </c>
       <c r="I74" s="51" t="inlineStr">
         <is>
-          <t>机器人技术实践</t>
+          <t>VR/AR交互开发、仿真可视化设计</t>
         </is>
       </c>
     </row>
@@ -7588,7 +7740,7 @@
       </c>
       <c r="H85" s="54" t="inlineStr">
         <is>
-          <t>具身智能实训室、具身智能实训室、集成电路与电子信息实训室</t>
+          <t>具身智能实训室、具身智能实训室、AIoT智能融合实训室</t>
         </is>
       </c>
       <c r="I85" s="54" t="inlineStr">
@@ -8012,7 +8164,7 @@
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>AI芯片设计工程师</t>
+          <t>AI芯片设计（应用）工程师</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
@@ -8027,7 +8179,7 @@
       </c>
       <c r="E5" s="39" t="inlineStr">
         <is>
-          <t>AI芯片设计工程师</t>
+          <t>AI芯片设计（应用）工程师</t>
         </is>
       </c>
       <c r="F5" s="39" t="inlineStr">
@@ -8037,7 +8189,7 @@
       </c>
       <c r="G5" s="39" t="inlineStr">
         <is>
-          <t>TPU异构算力与软硬协同实训室、洁净实验室1、洁净实验室2、集成电路与电子信息实训室</t>
+          <t>TPU异构算力与软硬协同实训室、洁净实验室、洁净实验室、AIoT智能融合实训室</t>
         </is>
       </c>
       <c r="H5" s="39" t="inlineStr">
@@ -8077,7 +8229,7 @@
       </c>
       <c r="G6" s="39" t="inlineStr">
         <is>
-          <t>AI4S实训室、TPU异构算力与软硬协同实训室、空天地一体实训室、高性能智算实训室</t>
+          <t>AI4S实训室、TPU异构算力与软硬协同实训室、虚拟仿真创新实训室、高性能智算实训室</t>
         </is>
       </c>
       <c r="H6" s="39" t="inlineStr">
@@ -8797,7 +8949,7 @@
       </c>
       <c r="G24" s="51" t="inlineStr">
         <is>
-          <t>人工智能应用开发实训室、智能边缘计算应用开发实训室、鸿蒙智联实训室</t>
+          <t>人工智能应用开发实训室、智能边缘计算应用开发实训室、鸿蒙物联网智能技术实训室</t>
         </is>
       </c>
       <c r="H24" s="51" t="inlineStr">
@@ -8852,7 +9004,7 @@
       </c>
       <c r="B26" s="51" t="inlineStr">
         <is>
-          <t>具身智能算法工程师</t>
+          <t>虚拟仿真工程师</t>
         </is>
       </c>
       <c r="C26" s="51" t="inlineStr">
@@ -8862,7 +9014,7 @@
       </c>
       <c r="D26" s="51" t="inlineStr">
         <is>
-          <t>具身智能算法工程师</t>
+          <t>虚拟仿真工程师</t>
         </is>
       </c>
       <c r="E26" s="51" t="inlineStr">
@@ -9077,7 +9229,7 @@
       </c>
       <c r="G31" s="54" t="inlineStr">
         <is>
-          <t>具身智能实训室、集成电路与电子信息实训室</t>
+          <t>具身智能实训室、AIoT智能融合实训室</t>
         </is>
       </c>
       <c r="H31" s="54" t="inlineStr">
@@ -10248,7 +10400,7 @@
       </c>
       <c r="B26" s="85" t="inlineStr">
         <is>
-          <t>鸿蒙智联实训室</t>
+          <t>鸿蒙物联网智能技术实训室</t>
         </is>
       </c>
       <c r="C26" s="61" t="inlineStr">
@@ -10393,7 +10545,7 @@
       </c>
       <c r="D29" s="85" t="inlineStr">
         <is>
-          <t>具身智能算法工程师</t>
+          <t>虚拟仿真工程师</t>
         </is>
       </c>
       <c r="E29" s="85" t="inlineStr">
@@ -11788,7 +11940,7 @@
       </c>
       <c r="D60" s="85" t="inlineStr">
         <is>
-          <t>具身智能算法工程师</t>
+          <t>虚拟仿真工程师</t>
         </is>
       </c>
       <c r="E60" s="85" t="inlineStr">
@@ -11958,7 +12110,7 @@
       </c>
       <c r="B64" s="85" t="inlineStr">
         <is>
-          <t>洁净实验室1</t>
+          <t>洁净实验室</t>
         </is>
       </c>
       <c r="C64" s="61" t="inlineStr">
@@ -11968,7 +12120,7 @@
       </c>
       <c r="D64" s="85" t="inlineStr">
         <is>
-          <t>AI芯片设计工程师</t>
+          <t>AI芯片设计（应用）工程师</t>
         </is>
       </c>
       <c r="E64" s="85" t="inlineStr">
@@ -12003,7 +12155,7 @@
       </c>
       <c r="B65" s="85" t="inlineStr">
         <is>
-          <t>洁净实验室2</t>
+          <t>洁净实验室</t>
         </is>
       </c>
       <c r="C65" s="61" t="inlineStr">
@@ -12013,7 +12165,7 @@
       </c>
       <c r="D65" s="85" t="inlineStr">
         <is>
-          <t>AI芯片设计工程师</t>
+          <t>AI芯片设计（应用）工程师</t>
         </is>
       </c>
       <c r="E65" s="85" t="inlineStr">
@@ -12048,7 +12200,7 @@
       </c>
       <c r="B66" s="85" t="inlineStr">
         <is>
-          <t>集成电路与电子信息实训室</t>
+          <t>AIoT智能融合实训室</t>
         </is>
       </c>
       <c r="C66" s="61" t="inlineStr">
@@ -12058,12 +12210,12 @@
       </c>
       <c r="D66" s="85" t="inlineStr">
         <is>
-          <t>AI芯片设计工程师</t>
+          <t>AI芯片设计（应用）工程师</t>
         </is>
       </c>
       <c r="E66" s="85" t="inlineStr">
         <is>
-          <t>芯片设计自动化综合项目、集成电路版图设计与验证、数字IC前端设计项目实战、VLSI前端设计(数字IC)、模拟集成电路设计</t>
+          <t>VLSI前端设计(数字IC)、数字IC前端设计项目实战、芯片设计自动化综合项目、集成电路版图设计与验证、SoC设计与ARM架构</t>
         </is>
       </c>
       <c r="F66" s="61" t="inlineStr">
@@ -12093,7 +12245,7 @@
       </c>
       <c r="B67" s="85" t="inlineStr">
         <is>
-          <t>集成电路与电子信息实训室</t>
+          <t>AIoT智能融合实训室</t>
         </is>
       </c>
       <c r="C67" s="61" t="inlineStr">
@@ -12108,7 +12260,7 @@
       </c>
       <c r="E67" s="85" t="inlineStr">
         <is>
-          <t>FPGA加速开发实训、FPGA开发与应用</t>
+          <t>SoC设计与ARM架构</t>
         </is>
       </c>
       <c r="F67" s="61" t="inlineStr">
@@ -12148,7 +12300,7 @@
       </c>
       <c r="D68" s="85" t="inlineStr">
         <is>
-          <t>AI芯片设计工程师</t>
+          <t>AI芯片设计（应用）工程师</t>
         </is>
       </c>
       <c r="E68" s="85" t="inlineStr">
@@ -12283,7 +12435,7 @@
       </c>
       <c r="D71" s="85" t="inlineStr">
         <is>
-          <t>具身智能算法工程师</t>
+          <t>虚拟仿真工程师</t>
         </is>
       </c>
       <c r="E71" s="85" t="inlineStr">
@@ -12993,7 +13145,7 @@
       </c>
       <c r="B87" s="85" t="inlineStr">
         <is>
-          <t>洁净实验室1</t>
+          <t>洁净实验室</t>
         </is>
       </c>
       <c r="C87" s="61" t="inlineStr">
@@ -13038,7 +13190,7 @@
       </c>
       <c r="B88" s="85" t="inlineStr">
         <is>
-          <t>洁净实验室2</t>
+          <t>洁净实验室</t>
         </is>
       </c>
       <c r="C88" s="61" t="inlineStr">
@@ -13732,7 +13884,7 @@
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>AI芯片设计工程师</t>
+          <t>AI芯片设计（应用）工程师</t>
         </is>
       </c>
       <c r="C5" s="38" t="inlineStr"/>
@@ -15962,7 +16114,7 @@
       </c>
       <c r="B26" s="51" t="inlineStr">
         <is>
-          <t>具身智能算法工程师</t>
+          <t>虚拟仿真工程师</t>
         </is>
       </c>
       <c r="C26" s="50" t="inlineStr"/>
@@ -16939,12 +17091,12 @@
       </c>
       <c r="C5" s="85" t="inlineStr">
         <is>
-          <t>AI芯片设计工程师/机器人×4等新增岗位对应课程体系待完善</t>
+          <t>AI芯片设计（应用）工程师/机器人×4等新增岗位对应课程体系待完善</t>
         </is>
       </c>
       <c r="D5" s="85" t="inlineStr">
         <is>
-          <t>集成电路与电子信息实训室、具身智能实训室等</t>
+          <t>AIoT智能融合实训室、具身智能实训室等</t>
         </is>
       </c>
       <c r="E5" s="85" t="inlineStr">
@@ -16974,7 +17126,7 @@
       </c>
       <c r="D6" s="85" t="inlineStr">
         <is>
-          <t>洁净实验室1/2</t>
+          <t>洁净实验室/2</t>
         </is>
       </c>
       <c r="E6" s="85" t="inlineStr">
@@ -16984,7 +17136,7 @@
       </c>
       <c r="F6" s="85" t="inlineStr">
         <is>
-          <t>需明确洁净实验室1和2各自的师资配置</t>
+          <t>需明确洁净实验室和2各自的师资配置</t>
         </is>
       </c>
     </row>
@@ -17125,4 +17277,3156 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="13" max="13"/>
+    <col width="32" customWidth="1" min="14" max="14"/>
+    <col width="32" customWidth="1" min="15" max="15"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="93" t="inlineStr">
+        <is>
+          <t>AI人才培养体系 — 岗位核心能力矩阵（30岗位 × 5大模块14项分项能力）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="94" t="inlineStr">
+        <is>
+          <t>●核心能力（红色）| ◐重要能力（金色）| ○了解即可 | —不适用  |  每个单元格：关联强度 + 岗位定制化说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="55" customHeight="1">
+      <c r="A4" s="95" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B4" s="95" t="inlineStr">
+        <is>
+          <t>岗位大类</t>
+        </is>
+      </c>
+      <c r="C4" s="95" t="inlineStr">
+        <is>
+          <t>岗位名称</t>
+        </is>
+      </c>
+      <c r="D4" s="95" t="inlineStr">
+        <is>
+          <t>1.算法与模型</t>
+        </is>
+      </c>
+      <c r="E4" s="95" t="inlineStr">
+        <is>
+          <t>2.编程与开发</t>
+        </is>
+      </c>
+      <c r="F4" s="95" t="inlineStr">
+        <is>
+          <t>3.数据处理</t>
+        </is>
+      </c>
+      <c r="G4" s="95" t="inlineStr">
+        <is>
+          <t>4.系统能力</t>
+        </is>
+      </c>
+      <c r="H4" s="95" t="inlineStr">
+        <is>
+          <t>5.项目交付能力</t>
+        </is>
+      </c>
+      <c r="I4" s="95" t="inlineStr">
+        <is>
+          <t>6.工具与平台使用能力</t>
+        </is>
+      </c>
+      <c r="J4" s="95" t="inlineStr">
+        <is>
+          <t>7.业务理解能力</t>
+        </is>
+      </c>
+      <c r="K4" s="95" t="inlineStr">
+        <is>
+          <t>8.解决方案能力</t>
+        </is>
+      </c>
+      <c r="L4" s="95" t="inlineStr">
+        <is>
+          <t>9.产品思维能力</t>
+        </is>
+      </c>
+      <c r="M4" s="95" t="inlineStr">
+        <is>
+          <t>10.沟通与协作能力</t>
+        </is>
+      </c>
+      <c r="N4" s="95" t="inlineStr">
+        <is>
+          <t>11.学习与创新能力</t>
+        </is>
+      </c>
+      <c r="O4" s="95" t="inlineStr">
+        <is>
+          <t>12.分析与解决问题能力</t>
+        </is>
+      </c>
+      <c r="P4" s="95" t="inlineStr">
+        <is>
+          <t>13.数据安全与隐私能力</t>
+        </is>
+      </c>
+      <c r="Q4" s="95" t="inlineStr">
+        <is>
+          <t>14.AI伦理</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="96" t="n"/>
+      <c r="B5" s="96" t="n"/>
+      <c r="C5" s="96" t="n"/>
+      <c r="D5" s="97" t="inlineStr">
+        <is>
+          <t>1.技术能力</t>
+        </is>
+      </c>
+      <c r="E5" s="96" t="n"/>
+      <c r="F5" s="96" t="n"/>
+      <c r="G5" s="97" t="inlineStr">
+        <is>
+          <t>2.工程与架构能力</t>
+        </is>
+      </c>
+      <c r="H5" s="96" t="n"/>
+      <c r="I5" s="96" t="n"/>
+      <c r="J5" s="97" t="inlineStr">
+        <is>
+          <t>3.行业与应用能力</t>
+        </is>
+      </c>
+      <c r="K5" s="96" t="n"/>
+      <c r="L5" s="96" t="n"/>
+      <c r="M5" s="97" t="inlineStr">
+        <is>
+          <t>4.专业素养与软技能</t>
+        </is>
+      </c>
+      <c r="N5" s="96" t="n"/>
+      <c r="O5" s="96" t="n"/>
+      <c r="P5" s="97" t="inlineStr">
+        <is>
+          <t>5.合规与安全能力</t>
+        </is>
+      </c>
+      <c r="Q5" s="96" t="n"/>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="98" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="99" t="inlineStr">
+        <is>
+          <t>基础设施类</t>
+        </is>
+      </c>
+      <c r="C6" s="100" t="inlineStr">
+        <is>
+          <t>智算中心运维工程师</t>
+        </is>
+      </c>
+      <c r="D6" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+了解常见AI算法的算力需求特征，能根据模型规模评估GPU资源分配</t>
+        </is>
+      </c>
+      <c r="E6" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+熟练使用Python编写运维脚本，掌握Shell/Ansible自动化工具，了解GPU编程基础</t>
+        </is>
+      </c>
+      <c r="F6" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+能处理集群监控数据、日志分析和性能指标数据的采集与可视化</t>
+        </is>
+      </c>
+      <c r="G6" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+精通Linux系统管理、GPU驱动配置、CUDA环境搭建、分布式存储和网络架构设计</t>
+        </is>
+      </c>
+      <c r="H6" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+参与基础设施建设项目管理，配合完成算力平台交付验收</t>
+        </is>
+      </c>
+      <c r="I6" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+精通Slurm/K8s等集群调度系统、Prometheus/Grafana监控、NVIDIA管理工具</t>
+        </is>
+      </c>
+      <c r="J6" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+了解AI训练/推理场景对算力的差异化需求</t>
+        </is>
+      </c>
+      <c r="K6" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+能根据业务需求提供基础算力资源配置方案</t>
+        </is>
+      </c>
+      <c r="L6" s="101" t="inlineStr">
+        <is>
+          <t>—不适用
+不直接参与产品设计</t>
+        </is>
+      </c>
+      <c r="M6" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+需与算法团队、开发团队协调算力资源，处理跨部门技术支持</t>
+        </is>
+      </c>
+      <c r="N6" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+跟踪GPU架构演进、算力调度新技术，持续优化集群效率</t>
+        </is>
+      </c>
+      <c r="O6" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+快速定位GPU故障、网络瓶颈、存储IO等系统级问题</t>
+        </is>
+      </c>
+      <c r="P6" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+负责集群访问控制、数据隔离、日志审计等基础设施安全</t>
+        </is>
+      </c>
+      <c r="Q6" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+了解算力资源公平分配原则</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="80" customHeight="1">
+      <c r="A7" s="104" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="105" t="inlineStr">
+        <is>
+          <t>基础设施类</t>
+        </is>
+      </c>
+      <c r="C7" s="106" t="inlineStr">
+        <is>
+          <t>AI芯片设计（应用）工程师</t>
+        </is>
+      </c>
+      <c r="D7" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+精通深度学习算法原理，理解模型计算图、算子特征，能进行算法-硬件协同优化</t>
+        </is>
+      </c>
+      <c r="E7" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+精通C/C++、Python，掌握HDL(Verilog/VHDL)、熟悉EDA工具链</t>
+        </is>
+      </c>
+      <c r="F7" s="108" t="inlineStr">
+        <is>
+          <t>○了解
+了解模型量化和数据格式对芯片性能的影响</t>
+        </is>
+      </c>
+      <c r="G7" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+深入理解芯片架构设计、指令集、缓存层次、片上互联，能进行架构级性能评估</t>
+        </is>
+      </c>
+      <c r="H7" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+参与芯片设计里程碑管理，配合流片验证和量产导入</t>
+        </is>
+      </c>
+      <c r="I7" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+精通EDA综合/仿真/验证工具、FPGA开发平台、AI编译器(TVM/MLIR等)</t>
+        </is>
+      </c>
+      <c r="J7" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+理解芯片应用场景需求（自动驾驶/数据中心/边缘设备等）</t>
+        </is>
+      </c>
+      <c r="K7" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+能基于业务需求设计芯片架构方案，评估PPA指标</t>
+        </is>
+      </c>
+      <c r="L7" s="108" t="inlineStr">
+        <is>
+          <t>○了解
+了解芯片产品化流程和市场定位</t>
+        </is>
+      </c>
+      <c r="M7" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+需与算法团队、流片团队、封测厂等多方协作</t>
+        </is>
+      </c>
+      <c r="N7" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+芯片架构和AI算法快速迭代，需持续跟踪前沿论文和业界动态</t>
+        </is>
+      </c>
+      <c r="O7" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+通过性能分析和仿真定位设计瓶颈，系统性优化架构</t>
+        </is>
+      </c>
+      <c r="P7" s="108" t="inlineStr">
+        <is>
+          <t>○了解
+了解芯片安全设计（可信执行环境、侧信道防护等）</t>
+        </is>
+      </c>
+      <c r="Q7" s="108" t="inlineStr">
+        <is>
+          <t>○了解
+关注芯片能效比，理解AI硬件的可持续发展</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="98" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="99" t="inlineStr">
+        <is>
+          <t>基础设施类</t>
+        </is>
+      </c>
+      <c r="C8" s="100" t="inlineStr">
+        <is>
+          <t>高性能计算工程师</t>
+        </is>
+      </c>
+      <c r="D8" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+理解并行计算模型(MAPReduce/BSP)，能分析算法并行度和通信复杂度</t>
+        </is>
+      </c>
+      <c r="E8" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+精通MPI/OpenMP/CUDA编程，熟练掌握Fortran/C++，了解GPU内核优化</t>
+        </is>
+      </c>
+      <c r="F8" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+处理大规模科学计算数据的I/O优化、并行文件系统操作</t>
+        </is>
+      </c>
+      <c r="G8" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+精通HPC集群架构、InfiniBand网络、并行文件系统(Lustre/GPFS)、作业调度</t>
+        </is>
+      </c>
+      <c r="H8" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+参与HPC项目建设与性能调优交付</t>
+        </is>
+      </c>
+      <c r="I8" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+精通性能分析工具(Profiling)、调试器、编译器优化选项和科学计算库</t>
+        </is>
+      </c>
+      <c r="J8" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+理解气象/生物/材料/金融等领域的科学计算需求特征</t>
+        </is>
+      </c>
+      <c r="K8" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+能设计面向特定领域的高性能计算方案</t>
+        </is>
+      </c>
+      <c r="L8" s="101" t="inlineStr">
+        <is>
+          <t>—不适用
+不直接参与产品设计</t>
+        </is>
+      </c>
+      <c r="M8" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+与科研团队协作优化计算任务</t>
+        </is>
+      </c>
+      <c r="N8" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+跟踪异构计算、量子计算等前沿计算范式</t>
+        </is>
+      </c>
+      <c r="O8" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+通过性能剖析定位计算瓶颈，系统性优化并行效率</t>
+        </is>
+      </c>
+      <c r="P8" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+了解HPC环境的数据隔离和访问控制</t>
+        </is>
+      </c>
+      <c r="Q8" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+关注绿色计算，优化算力能耗比</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="80" customHeight="1">
+      <c r="A9" s="104" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="105" t="inlineStr">
+        <is>
+          <t>基础设施类</t>
+        </is>
+      </c>
+      <c r="C9" s="106" t="inlineStr">
+        <is>
+          <t>MLOps工程师</t>
+        </is>
+      </c>
+      <c r="D9" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+理解模型训练/推理流程，能设计模型版本管理和实验追踪体系</t>
+        </is>
+      </c>
+      <c r="E9" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+精通Python/Go/Shell，掌握Docker/K8s，熟悉CI/CD流水线构建</t>
+        </is>
+      </c>
+      <c r="F9" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+设计数据管道(Data Pipeline)、特征存储和训练数据版本管理</t>
+        </is>
+      </c>
+      <c r="G9" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+构建端到端MLOps平台架构，包括模型训练→验证→部署→监控全链路</t>
+        </is>
+      </c>
+      <c r="H9" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+作为ML系统工程化负责人，管控模型上线的进度、质量和风险</t>
+        </is>
+      </c>
+      <c r="I9" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+精通MLflow/Kubeflow/Airflow等平台，熟悉模型压缩/量化/蒸馏工具链</t>
+        </is>
+      </c>
+      <c r="J9" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+理解模型服务等级协议(SLA)和业务对模型性能的要求</t>
+        </is>
+      </c>
+      <c r="K9" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+设计模型工程化部署方案(在线/离线/边缘)，解决规模化落地问题</t>
+        </is>
+      </c>
+      <c r="L9" s="108" t="inlineStr">
+        <is>
+          <t>○了解
+了解ML平台产品化的用户体验需求</t>
+        </is>
+      </c>
+      <c r="M9" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+协调算法、后端、运维等多团队推动模型上线</t>
+        </is>
+      </c>
+      <c r="N9" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+MLOps工具链快速演进，需持续评估引入新技术</t>
+        </is>
+      </c>
+      <c r="O9" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+系统性排查模型推理延迟、吞吐瓶颈、漂移检测等技术问题</t>
+        </is>
+      </c>
+      <c r="P9" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+设计模型服务的数据脱敏、访问鉴权和审计机制</t>
+        </is>
+      </c>
+      <c r="Q9" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+建立模型偏见检测和可解释性监控流程</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="80" customHeight="1">
+      <c r="A10" s="98" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="99" t="inlineStr">
+        <is>
+          <t>基础设施类</t>
+        </is>
+      </c>
+      <c r="C10" s="100" t="inlineStr">
+        <is>
+          <t>AI平台SRE工程师</t>
+        </is>
+      </c>
+      <c r="D10" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+了解AI训练任务的资源消耗特征和容错需求</t>
+        </is>
+      </c>
+      <c r="E10" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+精通Python/Go，掌握自动化运维脚本开发，了解基础设施即代码(Terraform)</t>
+        </is>
+      </c>
+      <c r="F10" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+处理平台监控数据、告警数据和运维指标分析</t>
+        </is>
+      </c>
+      <c r="G10" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+精通分布式系统、云原生架构、微服务治理，设计高可用AI平台</t>
+        </is>
+      </c>
+      <c r="H10" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+负责AI平台的SLA保障、容量规划和稳定性治理</t>
+        </is>
+      </c>
+      <c r="I10" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+精通监控(Prometheus/Datadog)、日志(ELK)、链路追踪、自动扩缩容工具</t>
+        </is>
+      </c>
+      <c r="J10" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+理解不同AI业务线对平台稳定性和性能的差异化需求</t>
+        </is>
+      </c>
+      <c r="K10" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+设计故障自愈、灰度发布、流量管理等平台级解决方案</t>
+        </is>
+      </c>
+      <c r="L10" s="101" t="inlineStr">
+        <is>
+          <t>—不适用
+不直接参与产品设计</t>
+        </is>
+      </c>
+      <c r="M10" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+作为平台守护者，需协调业务、算法、基础架构等多方</t>
+        </is>
+      </c>
+      <c r="N10" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+跟踪SRE最佳实践和云原生技术演进</t>
+        </is>
+      </c>
+      <c r="O10" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+通过SLO/SLI分析定位平台瓶颈，制定稳定性改进方案</t>
+        </is>
+      </c>
+      <c r="P10" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+负责平台网络安全、身份认证和运行数据保护</t>
+        </is>
+      </c>
+      <c r="Q10" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+关注AI平台的资源公平调度</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="80" customHeight="1">
+      <c r="A11" s="104" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="105" t="inlineStr">
+        <is>
+          <t>数据类</t>
+        </is>
+      </c>
+      <c r="C11" s="106" t="inlineStr">
+        <is>
+          <t>AI训练师</t>
+        </is>
+      </c>
+      <c r="D11" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+精通大模型Prompt工程、RLHF/RLAIF对齐技术，理解Transformer架构和注意力机制</t>
+        </is>
+      </c>
+      <c r="E11" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+熟练使用Python进行模型微调和推理调用，掌握API集成和简单脚本开发</t>
+        </is>
+      </c>
+      <c r="F11" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+负责训练数据的筛选、清洗、标注规范制定和质量控制</t>
+        </is>
+      </c>
+      <c r="G11" s="108" t="inlineStr">
+        <is>
+          <t>○了解
+了解模型训练的算力需求和基本部署流程</t>
+        </is>
+      </c>
+      <c r="H11" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+管理大模型训练项目的迭代周期、评估标准和交付节奏</t>
+        </is>
+      </c>
+      <c r="I11" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+精通各类大模型平台(OpenAI/国产大模型API)、Prompt管理工具、评测框架</t>
+        </is>
+      </c>
+      <c r="J11" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+深入理解应用场景需求，将业务目标转化为模型训练目标</t>
+        </is>
+      </c>
+      <c r="K11" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+能设计基于大模型的业务解决方案，定义任务流程和评估指标</t>
+        </is>
+      </c>
+      <c r="L11" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+具备AI产品思维，能从用户体验角度优化模型交互效果</t>
+        </is>
+      </c>
+      <c r="M11" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+与算法工程师、产品经理协同优化模型输出质量</t>
+        </is>
+      </c>
+      <c r="N11" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+大模型技术日新月异，需快速掌握新模型能力边界和最佳实践</t>
+        </is>
+      </c>
+      <c r="O11" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+通过分析模型输出质量，定位问题根因并设计改进策略</t>
+        </is>
+      </c>
+      <c r="P11" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+训练数据脱敏处理，防止敏感信息泄露到模型输出</t>
+        </is>
+      </c>
+      <c r="Q11" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+在训练过程中主动识别和消除偏见、有害内容，确保模型输出合规</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="80" customHeight="1">
+      <c r="A12" s="98" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="99" t="inlineStr">
+        <is>
+          <t>数据类</t>
+        </is>
+      </c>
+      <c r="C12" s="100" t="inlineStr">
+        <is>
+          <t>数据标注工程师</t>
+        </is>
+      </c>
+      <c r="D12" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+了解基本AI概念，理解标注数据对模型训练质量的影响</t>
+        </is>
+      </c>
+      <c r="E12" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+会使用标注工具和简单脚本辅助标注，不要求深度编程</t>
+        </is>
+      </c>
+      <c r="F12" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+核心职责：掌握数据标注的全流程，包括规范理解、标注执行、交叉验证和质量检查</t>
+        </is>
+      </c>
+      <c r="G12" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+了解标注平台的基本操作和数据上传下载</t>
+        </is>
+      </c>
+      <c r="H12" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+按项目进度完成标注任务，保证标注数量和质量达标</t>
+        </is>
+      </c>
+      <c r="I12" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+精通各类标注工具(Label Studio/CVAT等)和标注管理平台</t>
+        </is>
+      </c>
+      <c r="J12" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+理解标注对象所属领域的业务背景，确保标注语义准确</t>
+        </is>
+      </c>
+      <c r="K12" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+能发现标注规范中的模糊点并提出改进建议</t>
+        </is>
+      </c>
+      <c r="L12" s="101" t="inlineStr">
+        <is>
+          <t>—不适用
+不直接参与产品设计</t>
+        </is>
+      </c>
+      <c r="M12" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+与标注团队和质检团队沟通标注规范，反馈异常样本</t>
+        </is>
+      </c>
+      <c r="N12" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+适应不同标注任务类型(图像/文本/视频/3D)，快速掌握新工具</t>
+        </is>
+      </c>
+      <c r="O12" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+能识别标注错误模式，提出批量修正策略</t>
+        </is>
+      </c>
+      <c r="P12" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+严格保密标注数据，防止数据泄露，遵守脱敏规范</t>
+        </is>
+      </c>
+      <c r="Q12" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+在标注过程中注意公平性和多样性，避免引入偏见标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="80" customHeight="1">
+      <c r="A13" s="104" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="105" t="inlineStr">
+        <is>
+          <t>数据类</t>
+        </is>
+      </c>
+      <c r="C13" s="106" t="inlineStr">
+        <is>
+          <t>NLP数据工程师</t>
+        </is>
+      </c>
+      <c r="D13" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+理解NLP算法(分词/NER/情感分析/大模型)对数据的格式和质量要求</t>
+        </is>
+      </c>
+      <c r="E13" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+精通Python，熟悉Spark/Hadoop大数据处理框架，掌握ETL管道开发</t>
+        </is>
+      </c>
+      <c r="F13" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+负责文本语料的采集、清洗、去重、分词、向量化全流程数据处理</t>
+        </is>
+      </c>
+      <c r="G13" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+设计并维护数据管道架构，确保数据流的可靠性和时效性</t>
+        </is>
+      </c>
+      <c r="H13" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+管理语料库建设进度，保障数据质量和交付周期</t>
+        </is>
+      </c>
+      <c r="I13" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+精通Elasticsearch/向量数据库(Milvus/Weaviate)、Kafka、Airflow等工具</t>
+        </is>
+      </c>
+      <c r="J13" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+理解NLP应用场景(搜索/问答/翻译/摘要)对语料的差异化需求</t>
+        </is>
+      </c>
+      <c r="K13" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+设计面向NLP任务的数据工程方案，解决数据稀疏、长尾等问题</t>
+        </is>
+      </c>
+      <c r="L13" s="108" t="inlineStr">
+        <is>
+          <t>—不适用
+不直接参与产品设计</t>
+        </is>
+      </c>
+      <c r="M13" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+与算法团队协同定义数据规范，与采集团队协调数据来源</t>
+        </is>
+      </c>
+      <c r="N13" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+跟踪大模型时代的语料工程新方法和向量检索新技术</t>
+        </is>
+      </c>
+      <c r="O13" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+分析语料质量问题，设计数据增强和清洗策略</t>
+        </is>
+      </c>
+      <c r="P13" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+处理文本数据时执行脱敏、合规审查，防止个人信息泄露</t>
+        </is>
+      </c>
+      <c r="Q13" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+关注语料数据的版权合规，避免使用有偏见的数据源</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="80" customHeight="1">
+      <c r="A14" s="98" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="99" t="inlineStr">
+        <is>
+          <t>数据类</t>
+        </is>
+      </c>
+      <c r="C14" s="100" t="inlineStr">
+        <is>
+          <t>数据分析师</t>
+        </is>
+      </c>
+      <c r="D14" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+掌握常用统计算法和机器学习方法(回归/聚类/分类)，能建模分析业务数据</t>
+        </is>
+      </c>
+      <c r="E14" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+熟练使用Python/SQL/R，能编写数据处理和分析脚本</t>
+        </is>
+      </c>
+      <c r="F14" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+精通数据采集、清洗、转换、聚合的全流程，熟练使用Pandas/SQL/Excel</t>
+        </is>
+      </c>
+      <c r="G14" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+了解数据仓库/数据湖的基本架构</t>
+        </is>
+      </c>
+      <c r="H14" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+独立完成分析报告撰写和汇报，保障分析结论的可操作性</t>
+        </is>
+      </c>
+      <c r="I14" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+精通BI工具(Tableau/PowerBI)、统计软件、数据可视化工具</t>
+        </is>
+      </c>
+      <c r="J14" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+深入理解业务指标体系、核心KPI和数据背后的业务逻辑</t>
+        </is>
+      </c>
+      <c r="K14" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+能基于数据分析发现业务问题并提出改进建议</t>
+        </is>
+      </c>
+      <c r="L14" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+具备数据驱动思维，能用数据支撑产品决策</t>
+        </is>
+      </c>
+      <c r="M14" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+需向非技术受众清晰传达分析结论，协调各部门数据需求</t>
+        </is>
+      </c>
+      <c r="N14" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+关注AI赋能数据分析的新工具和方法(如NL2SQL、智能BI)</t>
+        </is>
+      </c>
+      <c r="O14" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+通过数据洞察定位业务问题，系统性提出数据驱动的解决方案</t>
+        </is>
+      </c>
+      <c r="P14" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+遵守数据使用规范，执行必要的数据脱敏和权限管理</t>
+        </is>
+      </c>
+      <c r="Q14" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+了解数据使用中的偏见和公平性问题</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="80" customHeight="1">
+      <c r="A15" s="104" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="105" t="inlineStr">
+        <is>
+          <t>数据类</t>
+        </is>
+      </c>
+      <c r="C15" s="106" t="inlineStr">
+        <is>
+          <t>数据安全架构师</t>
+        </is>
+      </c>
+      <c r="D15" s="108" t="inlineStr">
+        <is>
+          <t>○了解
+了解AI安全相关算法(联邦学习/隐私计算/对抗检测)</t>
+        </is>
+      </c>
+      <c r="E15" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+具备安全工具开发能力，掌握Python/Go编写安全检测和审计脚本</t>
+        </is>
+      </c>
+      <c r="F15" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+设计敏感数据处理流程，包括分类分级、脱敏和全生命周期管理</t>
+        </is>
+      </c>
+      <c r="G15" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+设计企业级数据安全架构，包括零信任架构、加密体系、访问控制矩阵</t>
+        </is>
+      </c>
+      <c r="H15" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+管理数据安全项目的合规评估、安全加固和认证审计交付</t>
+        </is>
+      </c>
+      <c r="I15" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+精通数据安全工具(分类分级平台/DLP/SIEM/密钥管理系统)</t>
+        </is>
+      </c>
+      <c r="J15" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+深入理解行业数据安全法规(等保/GDPR/数据安全法)和业务合规要求</t>
+        </is>
+      </c>
+      <c r="K15" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+设计端到端数据安全解决方案，覆盖数据采集-传输-存储-使用-销毁</t>
+        </is>
+      </c>
+      <c r="L15" s="108" t="inlineStr">
+        <is>
+          <t>○了解
+了解数据安全产品的选型和集成需求</t>
+        </is>
+      </c>
+      <c r="M15" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+与业务、技术、法务多方协作推进安全合规落地</t>
+        </is>
+      </c>
+      <c r="N15" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+跟踪AI安全、隐私计算、量子安全等前沿安全技术</t>
+        </is>
+      </c>
+      <c r="O15" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+系统性评估安全风险，设计纵深防御方案</t>
+        </is>
+      </c>
+      <c r="P15" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+数据安全领域的核心专家，精通等保2.0/GDPR/数据分类分级/加密脱敏</t>
+        </is>
+      </c>
+      <c r="Q15" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+关注AI数据使用的合规边界，设计AI模型的可审计和可追溯机制</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="80" customHeight="1">
+      <c r="A16" s="98" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="99" t="inlineStr">
+        <is>
+          <t>技术类</t>
+        </is>
+      </c>
+      <c r="C16" s="100" t="inlineStr">
+        <is>
+          <t>AIGC算法工程师</t>
+        </is>
+      </c>
+      <c r="D16" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+精通扩散模型(Diffusion/GAN/VAE)、大模型生成架构、多模态生成(SDXL/Sora等)</t>
+        </is>
+      </c>
+      <c r="E16" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+精通Python/PyTorch，掌握模型训练工程(分布式训练/混合精度/梯度累积)</t>
+        </is>
+      </c>
+      <c r="F16" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+负责高质量训练数据的筛选、预处理和数据增强(图像对/文本-图像对构建)</t>
+        </is>
+      </c>
+      <c r="G16" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+理解GPU集群训练架构，能优化训练效率和显存使用</t>
+        </is>
+      </c>
+      <c r="H16" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+管理模型训练迭代周期，定义评测指标和基线，推动模型上线</t>
+        </is>
+      </c>
+      <c r="I16" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+精通ComfyUI/Stable Diffusion生态、模型微调工具(LoRA/DreamBooth)、推理优化</t>
+        </is>
+      </c>
+      <c r="J16" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+理解AIGC应用场景(内容生成/风格迁移/视频生成)的业务需求</t>
+        </is>
+      </c>
+      <c r="K16" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+针对特定业务场景设计生成模型方案，评估生成质量和效率</t>
+        </is>
+      </c>
+      <c r="L16" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+了解AIGC产品的用户体验和交互设计需求</t>
+        </is>
+      </c>
+      <c r="M16" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+与产品、运营协同定义生成效果标准，与后端协作部署模型服务</t>
+        </is>
+      </c>
+      <c r="N16" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+AIGC领域论文日新月异，需快速复现SOTA并探索创新方向</t>
+        </is>
+      </c>
+      <c r="O16" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+系统性分析生成质量问题(模糊/伪影/不协调)，设计针对性优化策略</t>
+        </is>
+      </c>
+      <c r="P16" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+防止生成模型泄露训练数据，保护版权内容</t>
+        </is>
+      </c>
+      <c r="Q16" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+关注Deepfake检测、生成内容标识、版权合规和内容安全</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="80" customHeight="1">
+      <c r="A17" s="104" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="105" t="inlineStr">
+        <is>
+          <t>技术类</t>
+        </is>
+      </c>
+      <c r="C17" s="106" t="inlineStr">
+        <is>
+          <t>多模态算法工程师</t>
+        </is>
+      </c>
+      <c r="D17" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+精通多模态融合架构(CLIP/BLIP/Llama-Vision)、跨模态对齐、视觉-语言预训练</t>
+        </is>
+      </c>
+      <c r="E17" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+精通Python/PyTorch，掌握多模态数据管道开发和分布式训练</t>
+        </is>
+      </c>
+      <c r="F17" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+负责图像/视频/文本/音频的多模态数据对齐、预处理和质量控制</t>
+        </is>
+      </c>
+      <c r="G17" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+理解多模态模型的计算瓶颈，能优化推理效率和显存占用</t>
+        </is>
+      </c>
+      <c r="H17" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+管理多模态模型的训练迭代和评测交付</t>
+        </is>
+      </c>
+      <c r="I17" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+精通多模态评估框架、推理加速(TensorRT/vLLM)、模型压缩量化</t>
+        </is>
+      </c>
+      <c r="J17" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+理解多模态应用场景(图文检索/视频理解/跨模态搜索)的需求差异</t>
+        </is>
+      </c>
+      <c r="K17" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+设计面向特定模态组合的融合方案和检索策略</t>
+        </is>
+      </c>
+      <c r="L17" s="108" t="inlineStr">
+        <is>
+          <t>○了解
+了解多模态交互产品的体验优化方向</t>
+        </is>
+      </c>
+      <c r="M17" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+协调单模态专家(视觉/NLP/语音)共同解决多模态对齐问题</t>
+        </is>
+      </c>
+      <c r="N17" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+多模态是AI前沿热点，需持续跟踪顶会论文和开源进展</t>
+        </is>
+      </c>
+      <c r="O17" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+诊断模态间对齐失败、表征退化等问题并提出解决方案</t>
+        </is>
+      </c>
+      <c r="P17" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+处理多源异构数据时确保数据合规和隐私保护</t>
+        </is>
+      </c>
+      <c r="Q17" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+关注多模态模型的安全性和鲁棒性，防止对抗攻击</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="80" customHeight="1">
+      <c r="A18" s="98" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="99" t="inlineStr">
+        <is>
+          <t>技术类</t>
+        </is>
+      </c>
+      <c r="C18" s="100" t="inlineStr">
+        <is>
+          <t>计算机视觉工程师</t>
+        </is>
+      </c>
+      <c r="D18" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+精通目标检测(YOLO/DETR)、图像分割(SAM/UNet)、3D视觉(NeRF/3DGS)、OCR等</t>
+        </is>
+      </c>
+      <c r="E18" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+精通Python/C++，掌握OpenCV、模型推理优化(TensorRT/ONNX)</t>
+        </is>
+      </c>
+      <c r="F18" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+负责图像/视频数据的标注规范制定、增强策略和质量控制</t>
+        </is>
+      </c>
+      <c r="G18" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+设计端到端视觉系统(采集→推理→后处理)，优化推理延迟和吞吐量</t>
+        </is>
+      </c>
+      <c r="H18" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+管理视觉模型的训练-验证-部署全流程，确保精度和速度指标达标</t>
+        </is>
+      </c>
+      <c r="I18" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+精通CUDA/TensorRT/ONNX推理加速、模型量化部署、边缘设备适配</t>
+        </is>
+      </c>
+      <c r="J18" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+理解视觉应用场景(工业质检/医学影像/安防监控)的特殊需求</t>
+        </is>
+      </c>
+      <c r="K18" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+针对特定场景设计视觉方案(相机选型/光照补偿/算法选型)</t>
+        </is>
+      </c>
+      <c r="L18" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+了解视觉产品的实时性和准确性体验要求</t>
+        </is>
+      </c>
+      <c r="M18" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+与硬件工程师、产品经理协作定义系统边界和验收标准</t>
+        </is>
+      </c>
+      <c r="N18" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+跟踪Vision Transformer、视觉基础模型等前沿方向</t>
+        </is>
+      </c>
+      <c r="O18" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+通过消融实验定位模型精度问题，系统性优化检测/分割效果</t>
+        </is>
+      </c>
+      <c r="P18" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+处理图像中的人脸、车牌等隐私信息需合规脱敏</t>
+        </is>
+      </c>
+      <c r="Q18" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+关注视觉系统中的偏见和公平性问题(人脸识别偏差等)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="80" customHeight="1">
+      <c r="A19" s="104" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="105" t="inlineStr">
+        <is>
+          <t>技术类</t>
+        </is>
+      </c>
+      <c r="C19" s="106" t="inlineStr">
+        <is>
+          <t>强化学习研究员</t>
+        </is>
+      </c>
+      <c r="D19" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+精通RL算法(PPO/SAC/DQN)、多智能体RL(MARL)、RLHF、模仿学习/逆RL</t>
+        </is>
+      </c>
+      <c r="E19" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+精通Python/C++，掌握仿真环境开发(Gym/Mujoco/IsaacGym)</t>
+        </is>
+      </c>
+      <c r="F19" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+处理奖励信号设计、轨迹数据收集和经验回放缓冲区管理</t>
+        </is>
+      </c>
+      <c r="G19" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+构建仿真到现实(Sim2Real)的实验平台和评测体系</t>
+        </is>
+      </c>
+      <c r="H19" s="108" t="inlineStr">
+        <is>
+          <t>○了解
+以研究探索为主，参与原型验证和论文发表</t>
+        </is>
+      </c>
+      <c r="I19" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+精通强化学习框架(Ray RLlib/Stable-Baselines3)、仿真平台</t>
+        </is>
+      </c>
+      <c r="J19" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+理解RL应用场景(机器人控制/游戏AI/自动驾驶/资源调度)的需求</t>
+        </is>
+      </c>
+      <c r="K19" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+将业务问题建模为MDP/POMDP，设计奖励函数和训练策略</t>
+        </is>
+      </c>
+      <c r="L19" s="108" t="inlineStr">
+        <is>
+          <t>—不适用
+以研究为导向，不直接参与产品设计</t>
+        </is>
+      </c>
+      <c r="M19" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+与算法团队共享研究成果，推动RL方法在实际场景的落地</t>
+        </is>
+      </c>
+      <c r="N19" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+RL是AI前沿研究热点，需持续跟踪顶会论文并探索创新</t>
+        </is>
+      </c>
+      <c r="O19" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+分析训练不稳定性、样本效率低等问题，设计创新算法改进</t>
+        </is>
+      </c>
+      <c r="P19" s="108" t="inlineStr">
+        <is>
+          <t>○了解
+了解RL训练数据的安全性和环境安全性</t>
+        </is>
+      </c>
+      <c r="Q19" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+关注RL Agent的安全对齐和可解释性问题</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="80" customHeight="1">
+      <c r="A20" s="98" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="99" t="inlineStr">
+        <is>
+          <t>技术类</t>
+        </is>
+      </c>
+      <c r="C20" s="100" t="inlineStr">
+        <is>
+          <t>大模型算法工程师</t>
+        </is>
+      </c>
+      <c r="D20" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+精通大语言模型预训练/增量预训练/SFT/RLHF，精通Transformer、MoE、注意力机制</t>
+        </is>
+      </c>
+      <c r="E20" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+精通Python/PyTorch/CUDA编程，掌握分布式训练(DeepSpeed/Megatron)</t>
+        </is>
+      </c>
+      <c r="F20" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+负责大规模语料的清洗、去重、质量筛选和Token化处理</t>
+        </is>
+      </c>
+      <c r="G20" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+理解大模型训练的并行策略(数据/模型/流水线并行)和显存优化</t>
+        </is>
+      </c>
+      <c r="H20" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+管理大模型训练迭代，定义评测基准(Benchmark)和验收标准</t>
+        </is>
+      </c>
+      <c r="I20" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+精通HuggingFace/DeepSpeed/Megatron/vLLM等大模型工具链和推理框架</t>
+        </is>
+      </c>
+      <c r="J20" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+理解不同应用场景对大模型能力(推理/创作/编码)的差异化需求</t>
+        </is>
+      </c>
+      <c r="K20" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+选择适合业务场景的大模型方案(微调/RAG/Agent)，设计评测方案</t>
+        </is>
+      </c>
+      <c r="L20" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+了解大模型产品的交互体验和能力边界</t>
+        </is>
+      </c>
+      <c r="M20" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+与训练师、产品、运营协作优化模型输出质量</t>
+        </is>
+      </c>
+      <c r="N20" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+大模型领域进展极快，需持续跟踪论文、开源模型和最佳实践</t>
+        </is>
+      </c>
+      <c r="O20" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+分析模型训练Loss曲线、评测Bad Case，系统性定位并解决问题</t>
+        </is>
+      </c>
+      <c r="P20" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+确保训练数据合规，防止模型泄露敏感信息</t>
+        </is>
+      </c>
+      <c r="Q20" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+负责模型安全对齐、价值观引导和有害输出防护</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="80" customHeight="1">
+      <c r="A21" s="104" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="105" t="inlineStr">
+        <is>
+          <t>营销/交付类</t>
+        </is>
+      </c>
+      <c r="C21" s="106" t="inlineStr">
+        <is>
+          <t>AI产品经理</t>
+        </is>
+      </c>
+      <c r="D21" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+理解主流AI算法能力边界和应用场景，能评估技术可行性</t>
+        </is>
+      </c>
+      <c r="E21" s="108" t="inlineStr">
+        <is>
+          <t>○了解
+了解基本编程概念和API调用，能与工程师有效沟通</t>
+        </is>
+      </c>
+      <c r="F21" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+理解数据驱动决策，能设计数据采集方案和指标体系</t>
+        </is>
+      </c>
+      <c r="G21" s="108" t="inlineStr">
+        <is>
+          <t>○了解
+了解AI系统基本架构(前端-后端-模型服务)，理解技术约束</t>
+        </is>
+      </c>
+      <c r="H21" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+负责AI产品的全生命周期管理，包括需求定义、迭代规划、上线运营</t>
+        </is>
+      </c>
+      <c r="I21" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+熟练使用产品管理工具、原型设计工具，了解AI平台能力</t>
+        </is>
+      </c>
+      <c r="J21" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+深入理解目标行业和用户需求，能将需求转化为产品功能和验收标准</t>
+        </is>
+      </c>
+      <c r="K21" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+设计AI产品方案，平衡技术能力和用户体验，定义产品路线图</t>
+        </is>
+      </c>
+      <c r="L21" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+核心能力：用户调研、需求分析、竞品分析、MVP设计、数据驱动迭代</t>
+        </is>
+      </c>
+      <c r="M21" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+作为产品负责人，协调技术、设计、运营、销售等多方</t>
+        </is>
+      </c>
+      <c r="N21" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+跟踪AI技术趋势和市场动态，发现产品创新机会</t>
+        </is>
+      </c>
+      <c r="O21" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+通过数据分析发现产品问题，提出优化方案</t>
+        </is>
+      </c>
+      <c r="P21" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+在产品设计阶段纳入隐私保护和合规要求</t>
+        </is>
+      </c>
+      <c r="Q21" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+在产品设计中前置考虑AI伦理、公平性、可解释性和内容安全</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="80" customHeight="1">
+      <c r="A22" s="98" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="99" t="inlineStr">
+        <is>
+          <t>营销/交付类</t>
+        </is>
+      </c>
+      <c r="C22" s="100" t="inlineStr">
+        <is>
+          <t>智算销售经理</t>
+        </is>
+      </c>
+      <c r="D22" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+了解基本AI概念和算力需求特征</t>
+        </is>
+      </c>
+      <c r="E22" s="101" t="inlineStr">
+        <is>
+          <t>—不适用
+不涉及编程开发</t>
+        </is>
+      </c>
+      <c r="F22" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+了解客户数据需求和基本的数据安全要求</t>
+        </is>
+      </c>
+      <c r="G22" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+理解智算中心架构和算力产品规格，能向客户讲解技术方案</t>
+        </is>
+      </c>
+      <c r="H22" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+管理销售项目全流程(商机挖掘-方案-报价-签约-回款)</t>
+        </is>
+      </c>
+      <c r="I22" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+熟练使用CRM系统、销售管理工具、方案演示工具</t>
+        </is>
+      </c>
+      <c r="J22" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+深入理解客户所在行业的AI算力需求和痛点</t>
+        </is>
+      </c>
+      <c r="K22" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+能基于客户需求匹配算力产品，配合技术团队输出解决方案</t>
+        </is>
+      </c>
+      <c r="L22" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+从市场反馈角度推动算力产品优化</t>
+        </is>
+      </c>
+      <c r="M22" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+核心能力：客户关系维护、商务谈判、资源协调、内部跨部门协作</t>
+        </is>
+      </c>
+      <c r="N22" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+跟踪算力市场动态和竞品策略</t>
+        </is>
+      </c>
+      <c r="O22" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+分析客户需求，设计有竞争力的商务方案</t>
+        </is>
+      </c>
+      <c r="P22" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+了解商务合作中的数据保密要求</t>
+        </is>
+      </c>
+      <c r="Q22" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+了解AI行业合规趋势</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="80" customHeight="1">
+      <c r="A23" s="104" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="105" t="inlineStr">
+        <is>
+          <t>营销/交付类</t>
+        </is>
+      </c>
+      <c r="C23" s="106" t="inlineStr">
+        <is>
+          <t>AI解决方案专家</t>
+        </is>
+      </c>
+      <c r="D23" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+理解主流AI算法能力，能评估方案的技术可行性和效果预期</t>
+        </is>
+      </c>
+      <c r="E23" s="108" t="inlineStr">
+        <is>
+          <t>○了解
+了解技术架构，能与开发团队有效沟通</t>
+        </is>
+      </c>
+      <c r="F23" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+理解客户数据现状，能设计数据治理和准备方案</t>
+        </is>
+      </c>
+      <c r="G23" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+精通AI系统架构设计，能规划端到端技术方案(数据-模型-应用-运维)</t>
+        </is>
+      </c>
+      <c r="H23" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+负责解决方案从设计到落地的全流程管理</t>
+        </is>
+      </c>
+      <c r="I23" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+熟悉各类AI平台和工具，能进行技术选型和PoC验证</t>
+        </is>
+      </c>
+      <c r="J23" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+深入理解客户行业业务，能将业务问题转化为AI解决方案需求</t>
+        </is>
+      </c>
+      <c r="K23" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+核心能力：需求分析→技术选型→架构设计→PoC验证→方案编写→答辩</t>
+        </is>
+      </c>
+      <c r="L23" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+将解决方案产品化，设计可复用的行业方案模板</t>
+        </is>
+      </c>
+      <c r="M23" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+对客户和内部团队的沟通能力要求极高，需用技术语言和业务语言双向沟通</t>
+        </is>
+      </c>
+      <c r="N23" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+跟踪AI技术进展，积累行业解决方案经验</t>
+        </is>
+      </c>
+      <c r="O23" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+系统性分析客户痛点，设计最优技术方案</t>
+        </is>
+      </c>
+      <c r="P23" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+在方案设计中纳入安全合规架构和数据保护措施</t>
+        </is>
+      </c>
+      <c r="Q23" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+在方案设计阶段前置考虑AI伦理和合规要求</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="80" customHeight="1">
+      <c r="A24" s="98" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="99" t="inlineStr">
+        <is>
+          <t>营销/交付类</t>
+        </is>
+      </c>
+      <c r="C24" s="100" t="inlineStr">
+        <is>
+          <t>智算项目交付经理</t>
+        </is>
+      </c>
+      <c r="D24" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+了解项目涉及的AI技术基本原理</t>
+        </is>
+      </c>
+      <c r="E24" s="101" t="inlineStr">
+        <is>
+          <t>—不适用
+不直接参与编程开发</t>
+        </is>
+      </c>
+      <c r="F24" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+了解项目中的数据需求和数据处理流程</t>
+        </is>
+      </c>
+      <c r="G24" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+理解智算系统架构，能有效协调技术资源解决部署问题</t>
+        </is>
+      </c>
+      <c r="H24" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+核心能力：项目管理(PMP)、进度管控、风险管控、资源协调、验收交付</t>
+        </is>
+      </c>
+      <c r="I24" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+熟练使用项目管理工具(Jira/MS Project)、文档协作工具</t>
+        </is>
+      </c>
+      <c r="J24" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+理解客户业务需求和项目目标的对应关系</t>
+        </is>
+      </c>
+      <c r="K24" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+配合技术团队理解解决方案</t>
+        </is>
+      </c>
+      <c r="L24" s="101" t="inlineStr">
+        <is>
+          <t>—不适用
+不直接参与产品设计</t>
+        </is>
+      </c>
+      <c r="M24" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+核心能力：干系人管理、跨团队协调、客户沟通、冲突解决</t>
+        </is>
+      </c>
+      <c r="N24" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+了解行业动态和新项目管理方法</t>
+        </is>
+      </c>
+      <c r="O24" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+快速识别项目风险，制定应对策略</t>
+        </is>
+      </c>
+      <c r="P24" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+确保项目执行过程中的数据安全合规</t>
+        </is>
+      </c>
+      <c r="Q24" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+了解项目交付中的合规要求</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="80" customHeight="1">
+      <c r="A25" s="104" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="105" t="inlineStr">
+        <is>
+          <t>营销/交付类</t>
+        </is>
+      </c>
+      <c r="C25" s="106" t="inlineStr">
+        <is>
+          <t>AIGC内容运营</t>
+        </is>
+      </c>
+      <c r="D25" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+理解AIGC模型(文本/图像/视频生成)的能力边界和最佳使用方式</t>
+        </is>
+      </c>
+      <c r="E25" s="108" t="inlineStr">
+        <is>
+          <t>○了解
+会使用API调用和低代码工具，不要求深度编程</t>
+        </is>
+      </c>
+      <c r="F25" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+分析内容运营数据(流量/互动/转化)，用数据驱动内容策略优化</t>
+        </is>
+      </c>
+      <c r="G25" s="108" t="inlineStr">
+        <is>
+          <t>○了解
+了解内容管理平台和发布系统的基本操作</t>
+        </is>
+      </c>
+      <c r="H25" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+管理内容排期、专题策划和运营活动执行</t>
+        </is>
+      </c>
+      <c r="I25" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+精通各类AIGC工具(Midjourney/ChatGPT/即梦等)、内容管理和排版工具</t>
+        </is>
+      </c>
+      <c r="J25" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+深入理解目标用户需求、内容消费习惯和行业内容趋势</t>
+        </is>
+      </c>
+      <c r="K25" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+设计AIGC赋能的内容生产流程和运营策略</t>
+        </is>
+      </c>
+      <c r="L25" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+核心能力：内容策划、用户调研、热点判断、数据驱动运营、A/B测试</t>
+        </is>
+      </c>
+      <c r="M25" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+与设计、技术团队协作，推动AIGC工具在内容生产中的应用</t>
+        </is>
+      </c>
+      <c r="N25" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+AIGC工具迭代极快，需快速掌握新工具并探索创意应用</t>
+        </is>
+      </c>
+      <c r="O25" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+通过数据分析定位内容问题，优化运营策略</t>
+        </is>
+      </c>
+      <c r="P25" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+运营中注意用户数据保护和内容版权合规</t>
+        </is>
+      </c>
+      <c r="Q25" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+标注AI生成内容、防止虚假信息传播、关注内容版权和合规</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="80" customHeight="1">
+      <c r="A26" s="98" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="99" t="inlineStr">
+        <is>
+          <t>应用/开发类</t>
+        </is>
+      </c>
+      <c r="C26" s="100" t="inlineStr">
+        <is>
+          <t>AI解决方案架构师</t>
+        </is>
+      </c>
+      <c r="D26" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+理解主流AI算法的性能特征、部署约束和能力边界，指导技术选型</t>
+        </is>
+      </c>
+      <c r="E26" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+掌握原型验证开发能力，能评估技术方案可行性</t>
+        </is>
+      </c>
+      <c r="F26" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+设计数据架构方案，包括数据流、存储策略和治理框架</t>
+        </is>
+      </c>
+      <c r="G26" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+精通分布式系统设计、微服务架构、高可用方案，能设计企业级AI系统架构</t>
+        </is>
+      </c>
+      <c r="H26" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+负责架构方案的可行性分析、实施路径规划和落地交付</t>
+        </is>
+      </c>
+      <c r="I26" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+精通云平台(AWS/阿里云/华为云)AI服务、中间件选型和集成方案</t>
+        </is>
+      </c>
+      <c r="J26" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+深入理解客户业务战略，能将业务目标转化为技术架构蓝图</t>
+        </is>
+      </c>
+      <c r="K26" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+核心能力：架构设计→技术选型→可行性分析→性能评估→实施规划</t>
+        </is>
+      </c>
+      <c r="L26" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+从架构层面考虑系统的可扩展性、可维护性和演进路线</t>
+        </is>
+      </c>
+      <c r="M26" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+作为技术架构桥梁，需同时面向技术团队和客户高管进行方案沟通</t>
+        </is>
+      </c>
+      <c r="N26" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+跟踪前沿架构模式(如LLMOps、Agent架构)并评估引入可行性</t>
+        </is>
+      </c>
+      <c r="O26" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+系统性评估技术方案的复杂度、风险和瓶颈，设计架构优化路径</t>
+        </is>
+      </c>
+      <c r="P26" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+在架构设计中融入安全架构(零信任/加密/审计)和合规要求</t>
+        </is>
+      </c>
+      <c r="Q26" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+架构层面考虑AI可解释性、公平性和审计能力</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="80" customHeight="1">
+      <c r="A27" s="104" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="105" t="inlineStr">
+        <is>
+          <t>应用/开发类</t>
+        </is>
+      </c>
+      <c r="C27" s="106" t="inlineStr">
+        <is>
+          <t>LLM应用开发工程师</t>
+        </is>
+      </c>
+      <c r="D27" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+理解大模型架构原理、Token化、上下文窗口、推理特性，能设计Prompt策略</t>
+        </is>
+      </c>
+      <c r="E27" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+精通Python/TypeScript，掌握后端(FastAPI/Django)和前端开发、API集成</t>
+        </is>
+      </c>
+      <c r="F27" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+设计RAG系统的文档处理管道(解析/分块/向量化/检索)</t>
+        </is>
+      </c>
+      <c r="G27" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+设计Agent系统的消息队列、记忆管理和工具调用架构</t>
+        </is>
+      </c>
+      <c r="H27" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+管理LLM应用从原型到上线的全流程开发</t>
+        </is>
+      </c>
+      <c r="I27" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+精通LangChain/LlamaIndex/Dify框架、向量数据库、模型API(SDK/REST)</t>
+        </is>
+      </c>
+      <c r="J27" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+理解LLM应用场景(智能客服/文档问答/代码助手)的需求差异</t>
+        </is>
+      </c>
+      <c r="K27" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+设计基于LLM的应用方案(RAG/Agent/Workflow)，平衡效果和成本</t>
+        </is>
+      </c>
+      <c r="L27" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+关注AI应用的用户体验和交互设计</t>
+        </is>
+      </c>
+      <c r="M27" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+与算法工程师协作优化Prompt和模型调用策略</t>
+        </is>
+      </c>
+      <c r="N27" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+LLM应用开发框架日新月异，需快速评估引入新工具和新模式</t>
+        </is>
+      </c>
+      <c r="O27" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+诊断Agent执行链路中的问题(检索质量/幻觉/延迟)，持续优化</t>
+        </is>
+      </c>
+      <c r="P27" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+防止LLM应用泄露企业知识库中的敏感信息</t>
+        </is>
+      </c>
+      <c r="Q27" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+设计LLM输出的安全过滤和事实性校验机制</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="80" customHeight="1">
+      <c r="A28" s="98" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="99" t="inlineStr">
+        <is>
+          <t>应用/开发类</t>
+        </is>
+      </c>
+      <c r="C28" s="100" t="inlineStr">
+        <is>
+          <t>虚拟仿真工程师</t>
+        </is>
+      </c>
+      <c r="D28" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+精通数字孪生建模算法、仿真引擎算法、物理仿真模型、交互设计算法</t>
+        </is>
+      </c>
+      <c r="E28" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+精通Python/C++，掌握仿真平台开发(Unity/Unreal/Gazebo)和可视化编程</t>
+        </is>
+      </c>
+      <c r="F28" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+处理传感器数据融合(SLAM/IMU/视觉)、物理环境建模数据</t>
+        </is>
+      </c>
+      <c r="G28" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+设计数字孪生系统架构(虚实同步/实时仿真/大规模场景渲染)</t>
+        </is>
+      </c>
+      <c r="H28" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+管理仿真项目从需求建模→场景构建→验证→交付的全流程</t>
+        </is>
+      </c>
+      <c r="I28" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+精通数字孪生/仿真平台(Unity/Unreal/Gazebo/PreScan)、3D建模工具</t>
+        </is>
+      </c>
+      <c r="J28" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+理解仿真应用领域(工业制造/城市规划/医疗教学)的业务需求</t>
+        </is>
+      </c>
+      <c r="K28" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+设计面向特定行业的数字孪生仿真解决方案</t>
+        </is>
+      </c>
+      <c r="L28" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+了解仿真系统的用户体验和交互设计</t>
+        </is>
+      </c>
+      <c r="M28" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+与行业专家协作理解业务场景，与开发团队协作实现仿真系统</t>
+        </is>
+      </c>
+      <c r="N28" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+跟踪数字孪生、AIGC+3D生成等前沿仿真技术</t>
+        </is>
+      </c>
+      <c r="O28" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+分析仿真精度问题，优化模型参数和物理引擎配置</t>
+        </is>
+      </c>
+      <c r="P28" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+了解仿真环境中的数据安全要求</t>
+        </is>
+      </c>
+      <c r="Q28" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+关注仿真系统的可信度和误导风险</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="80" customHeight="1">
+      <c r="A29" s="104" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="105" t="inlineStr">
+        <is>
+          <t>应用/开发类</t>
+        </is>
+      </c>
+      <c r="C29" s="106" t="inlineStr">
+        <is>
+          <t>自动驾驶算法工程师</t>
+        </is>
+      </c>
+      <c r="D29" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+精通感知算法(2D/3D目标检测/语义分割/车道线检测)、路径规划(DRL/A*)、控制(MPC)</t>
+        </is>
+      </c>
+      <c r="E29" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+精通C++/Python，掌握ROS2开发框架和自动驾驶中间件</t>
+        </is>
+      </c>
+      <c r="F29" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+处理传感器数据融合(激光雷达/摄像头/毫米波雷达)、数据标注和场景库构建</t>
+        </is>
+      </c>
+      <c r="G29" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+设计自动驾驶软件架构(感知-规划-控制)，确保实时性和安全性</t>
+        </is>
+      </c>
+      <c r="H29" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+管理算法模块的迭代开发、仿真验证和实车测试交付</t>
+        </is>
+      </c>
+      <c r="I29" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+精通仿真平台(CARLA/PreScan)、ROS2/Autoware、量化部署工具</t>
+        </is>
+      </c>
+      <c r="J29" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+理解自动驾驶应用场景(L4 Robotaxi/高速NOA/泊车)的差异化需求</t>
+        </is>
+      </c>
+      <c r="K29" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+针对特定ODD(运行设计域)设计算法方案，平衡安全性和效率</t>
+        </is>
+      </c>
+      <c r="L29" s="108" t="inlineStr">
+        <is>
+          <t>○了解
+了解自动驾驶产品功能和用户体验</t>
+        </is>
+      </c>
+      <c r="M29" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+与车辆工程、传感器、验证团队紧密协作</t>
+        </is>
+      </c>
+      <c r="N29" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+跟踪端到端自动驾驶、BEV/Transformer感知等前沿方向</t>
+        </is>
+      </c>
+      <c r="O29" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+通过仿真和数据分析定位Corner Case，系统性改进算法</t>
+        </is>
+      </c>
+      <c r="P29" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+车辆数据采集和传输的安全合规，地图数据保密</t>
+        </is>
+      </c>
+      <c r="Q29" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+自动驾驶安全攸关，需严格确保系统安全性和道德决策</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="80" customHeight="1">
+      <c r="A30" s="98" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="99" t="inlineStr">
+        <is>
+          <t>应用/开发类</t>
+        </is>
+      </c>
+      <c r="C30" s="100" t="inlineStr">
+        <is>
+          <t>医疗AI研发工程师</t>
+        </is>
+      </c>
+      <c r="D30" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+精通医学影像AI(CNN/Transformer/分割)、临床NLP(实体识别/关系抽取)、多模态医疗AI</t>
+        </is>
+      </c>
+      <c r="E30" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+精通Python/C++，掌握医学影像处理工具(ITK/SimpleITK/DICOM库)</t>
+        </is>
+      </c>
+      <c r="F30" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+处理多源医疗数据(DICOM影像/电子病历/基因组)，严格的数据标准化和质控</t>
+        </is>
+      </c>
+      <c r="G30" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+设计医疗AI系统的部署架构，适配医院PACS/EMR系统集成</t>
+        </is>
+      </c>
+      <c r="H30" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+管理医疗AI产品从研发到临床试验、注册审批的全流程交付</t>
+        </is>
+      </c>
+      <c r="I30" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+精通MONAI/nnU-Net等医疗AI框架、DICOM工具链、联邦学习平台</t>
+        </is>
+      </c>
+      <c r="J30" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+深入理解医疗领域知识(解剖学/病理学/临床路径)和医院信息化流程</t>
+        </is>
+      </c>
+      <c r="K30" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+设计面向特定临床场景的AI辅助诊断/治疗解决方案</t>
+        </is>
+      </c>
+      <c r="L30" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+考虑临床工作流程中的产品易用性和医生交互体验</t>
+        </is>
+      </c>
+      <c r="M30" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+与临床医生、法规专家、医院IT团队紧密协作</t>
+        </is>
+      </c>
+      <c r="N30" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+跟踪医学AI前沿和监管政策动态</t>
+        </is>
+      </c>
+      <c r="O30" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+分析临床验证数据，系统性改进模型在真实临床场景的表现</t>
+        </is>
+      </c>
+      <c r="P30" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+医疗数据高度敏感，精通数据脱敏、HIPAA/等保合规、联邦学习</t>
+        </is>
+      </c>
+      <c r="Q30" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+医疗AI涉及患者生命安全，需严格遵守伦理审查和可解释性要求</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="80" customHeight="1">
+      <c r="A31" s="104" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="105" t="inlineStr">
+        <is>
+          <t>机器人技术类</t>
+        </is>
+      </c>
+      <c r="C31" s="106" t="inlineStr">
+        <is>
+          <t>机器人应用工程师</t>
+        </is>
+      </c>
+      <c r="D31" s="108" t="inlineStr">
+        <is>
+          <t>○了解
+了解基本的运动控制和路径规划算法</t>
+        </is>
+      </c>
+      <c r="E31" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+掌握机器人编程(示教器/ROS)、PLC编程和简单脚本开发</t>
+        </is>
+      </c>
+      <c r="F31" s="108" t="inlineStr">
+        <is>
+          <t>○了解
+处理基本的传感器数据和运行参数</t>
+        </is>
+      </c>
+      <c r="G31" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+理解机器人系统架构(控制器/驱动器/末端执行器/安全系统)</t>
+        </is>
+      </c>
+      <c r="H31" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+核心能力：现场调试→工艺优化→验收交付→运维支持的全流程交付</t>
+        </is>
+      </c>
+      <c r="I31" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+精通主流机器人品牌编程平台、调试工具、仿真软件</t>
+        </is>
+      </c>
+      <c r="J31" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+深入理解产线工艺要求和行业应用场景(焊接/装配/搬运等)</t>
+        </is>
+      </c>
+      <c r="K31" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+针对特定应用场景设计机器人工作站方案</t>
+        </is>
+      </c>
+      <c r="L31" s="108" t="inlineStr">
+        <is>
+          <t>—不适用
+不直接参与产品设计</t>
+        </is>
+      </c>
+      <c r="M31" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+与工艺工程师、电气工程师、客户现场团队协作</t>
+        </is>
+      </c>
+      <c r="N31" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+适应不同品牌和型号的机器人，快速掌握新应用工艺</t>
+        </is>
+      </c>
+      <c r="O31" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+快速诊断现场故障(机械/电气/程序)，制定修复方案</t>
+        </is>
+      </c>
+      <c r="P31" s="108" t="inlineStr">
+        <is>
+          <t>○了解
+了解工业现场的数据安全和操作安全规范</t>
+        </is>
+      </c>
+      <c r="Q31" s="108" t="inlineStr">
+        <is>
+          <t>○了解
+关注人机协作安全</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="80" customHeight="1">
+      <c r="A32" s="98" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="99" t="inlineStr">
+        <is>
+          <t>机器人技术类</t>
+        </is>
+      </c>
+      <c r="C32" s="100" t="inlineStr">
+        <is>
+          <t>机器人算法工程师</t>
+        </is>
+      </c>
+      <c r="D32" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+精通视觉感知(2D/3D检测)、SLAM导航(ORB-SLAM/Cartographer)、轨迹规划(RRT/MPC)、力控算法</t>
+        </is>
+      </c>
+      <c r="E32" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+精通C++/Python，掌握ROS2开发、嵌入式编程和实时控制</t>
+        </is>
+      </c>
+      <c r="F32" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+处理传感器数据融合(激光雷达/深度相机/IMU)、点云处理和SLAM建图</t>
+        </is>
+      </c>
+      <c r="G32" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+设计机器人软件架构(感知→决策→控制)，确保实时性和鲁棒性</t>
+        </is>
+      </c>
+      <c r="H32" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+管理算法模块的开发-仿真-实车验证迭代周期</t>
+        </is>
+      </c>
+      <c r="I32" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+精通ROS2/Gazebo仿真、OpenCV/PCL、嵌入式开发工具</t>
+        </is>
+      </c>
+      <c r="J32" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+理解机器人应用场景(工业/服务/物流)的差异化技术需求</t>
+        </is>
+      </c>
+      <c r="K32" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+针对特定场景设计算法方案(导航/抓取/人机协作)</t>
+        </is>
+      </c>
+      <c r="L32" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+了解机器人的用户体验和交互设计</t>
+        </is>
+      </c>
+      <c r="M32" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+与机械工程师、嵌入式工程师、应用工程师协作</t>
+        </is>
+      </c>
+      <c r="N32" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+跟踪具身智能、多模态机器人控制等前沿方向</t>
+        </is>
+      </c>
+      <c r="O32" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+通过仿真和实车数据分析定位算法问题，持续优化</t>
+        </is>
+      </c>
+      <c r="P32" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+了解机器人系统的网络安全要求</t>
+        </is>
+      </c>
+      <c r="Q32" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+关注人机协作中的安全性、机器人的社会影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="80" customHeight="1">
+      <c r="A33" s="104" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="105" t="inlineStr">
+        <is>
+          <t>机器人技术类</t>
+        </is>
+      </c>
+      <c r="C33" s="106" t="inlineStr">
+        <is>
+          <t>机器人软件工程师</t>
+        </is>
+      </c>
+      <c r="D33" s="108" t="inlineStr">
+        <is>
+          <t>○了解
+了解基本的运动控制和规划算法原理</t>
+        </is>
+      </c>
+      <c r="E33" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+精通C++/Python，掌握ROS2开发、嵌入式(Linux/RTOS)和通信协议(DDS/OPC-UA)</t>
+        </is>
+      </c>
+      <c r="F33" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+处理机器人传感器数据的接口开发、数据协议解析和传输优化</t>
+        </is>
+      </c>
+      <c r="G33" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+设计机器人软件系统架构(模块化/中间件/实时调度)，确保系统稳定性</t>
+        </is>
+      </c>
+      <c r="H33" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+管理软件模块的开发-集成-测试-部署全流程</t>
+        </is>
+      </c>
+      <c r="I33" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+精通ROS2/CI-CD/版本管理、嵌入式IDE、仿真工具</t>
+        </is>
+      </c>
+      <c r="J33" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+理解机器人产品的功能需求和软件规格</t>
+        </is>
+      </c>
+      <c r="K33" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+设计软件架构方案(功能安全/实时性/可扩展性)</t>
+        </is>
+      </c>
+      <c r="L33" s="108" t="inlineStr">
+        <is>
+          <t>○了解
+了解机器人产品的软件用户体验</t>
+        </is>
+      </c>
+      <c r="M33" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+与算法工程师、硬件工程师紧密协作完成系统集成</t>
+        </is>
+      </c>
+      <c r="N33" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+跟踪机器人操作系统和中间件技术演进</t>
+        </is>
+      </c>
+      <c r="O33" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+通过日志分析、调试工具定位软件Bug和性能瓶颈</t>
+        </is>
+      </c>
+      <c r="P33" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+设计机器人通信加密、固件安全和访问控制</t>
+        </is>
+      </c>
+      <c r="Q33" s="108" t="inlineStr">
+        <is>
+          <t>○了解
+关注机器人的安全标准(ISO 10218/TS 15066)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="80" customHeight="1">
+      <c r="A34" s="98" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" s="99" t="inlineStr">
+        <is>
+          <t>机器人技术类</t>
+        </is>
+      </c>
+      <c r="C34" s="100" t="inlineStr">
+        <is>
+          <t>机器人系统集成工程师</t>
+        </is>
+      </c>
+      <c r="D34" s="101" t="inlineStr">
+        <is>
+          <t>—不适用
+不涉及算法开发</t>
+        </is>
+      </c>
+      <c r="E34" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+掌握机器人编程、PLC编程和HMI组态，了解基础脚本开发</t>
+        </is>
+      </c>
+      <c r="F34" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+了解产线数据和MES系统的基本交互</t>
+        </is>
+      </c>
+      <c r="G34" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+核心能力：设计机器人集成方案(工作站/产线/工厂级)，统筹机械/电气/软件系统</t>
+        </is>
+      </c>
+      <c r="H34" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+核心能力：项目规划→方案设计→采购→安装调试→验收交付→运维交接</t>
+        </is>
+      </c>
+      <c r="I34" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+精通仿真规划(RobotStudio/Process Simulate)、电气设计和项目管理工具</t>
+        </is>
+      </c>
+      <c r="J34" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+深入理解客户行业工艺流程、产能需求和品质标准</t>
+        </is>
+      </c>
+      <c r="K34" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+设计面向特定行业的机器人集成方案(焊接/涂装/装配/码垛等)</t>
+        </is>
+      </c>
+      <c r="L34" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+了解标准工作站和模块化产品思路</t>
+        </is>
+      </c>
+      <c r="M34" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+作为项目核心，需协调客户、机械/电气/软件供应商、施工团队</t>
+        </is>
+      </c>
+      <c r="N34" s="102" t="inlineStr">
+        <is>
+          <t>◐重要
+学习新行业工艺和新设备集成方案</t>
+        </is>
+      </c>
+      <c r="O34" s="103" t="inlineStr">
+        <is>
+          <t>●核心
+快速诊断集成调试中的综合问题(机械干涉/电气故障/程序异常)</t>
+        </is>
+      </c>
+      <c r="P34" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+了解工业网络安全和数据保护要求</t>
+        </is>
+      </c>
+      <c r="Q34" s="101" t="inlineStr">
+        <is>
+          <t>○了解
+关注工业机器人的安全规范和标准</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="80" customHeight="1">
+      <c r="A35" s="104" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="105" t="inlineStr">
+        <is>
+          <t>机器人技术类</t>
+        </is>
+      </c>
+      <c r="C35" s="106" t="inlineStr">
+        <is>
+          <t>机器人运维工程师</t>
+        </is>
+      </c>
+      <c r="D35" s="108" t="inlineStr">
+        <is>
+          <t>—不适用
+不涉及算法开发</t>
+        </is>
+      </c>
+      <c r="E35" s="108" t="inlineStr">
+        <is>
+          <t>○了解
+了解基本的机器人编程和脚本调试</t>
+        </is>
+      </c>
+      <c r="F35" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+分析设备运行数据(振动/温度/电流)，建立预防性维护数据模型</t>
+        </is>
+      </c>
+      <c r="G35" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+精通机器人系统各组件(控制器/驱动/减速器/末端)的运维知识</t>
+        </is>
+      </c>
+      <c r="H35" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+管理维保计划执行、备件管理和停机时间控制</t>
+        </is>
+      </c>
+      <c r="I35" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+精通诊断工具(示波器/万用表/专用调试工具)、备件管理系统、SCADA</t>
+        </is>
+      </c>
+      <c r="J35" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+理解产线工艺和设备对生产的影响，优化维保策略</t>
+        </is>
+      </c>
+      <c r="K35" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+设计设备运维方案(预防性维护/预测性维护/故障应急预案)</t>
+        </is>
+      </c>
+      <c r="L35" s="108" t="inlineStr">
+        <is>
+          <t>—不适用
+不直接参与产品设计</t>
+        </is>
+      </c>
+      <c r="M35" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+与生产部门、设备供应商协调维保计划</t>
+        </is>
+      </c>
+      <c r="N35" s="109" t="inlineStr">
+        <is>
+          <t>◐重要
+跟踪智能运维(Predictive Maintenance)和数字孪生维护新技术</t>
+        </is>
+      </c>
+      <c r="O35" s="107" t="inlineStr">
+        <is>
+          <t>●核心
+快速诊断设备故障根因(机械/电气/程序)，制定修复和预防措施</t>
+        </is>
+      </c>
+      <c r="P35" s="108" t="inlineStr">
+        <is>
+          <t>○了解
+了解工业数据安全和设备访问安全</t>
+        </is>
+      </c>
+      <c r="Q35" s="108" t="inlineStr">
+        <is>
+          <t>○了解
+关注工业机器人安全操作规范</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="M5:O5"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="A2:P2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>